--- a/rapporten/investeerder.xlsx
+++ b/rapporten/investeerder.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overzicht" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verdeling" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uitleg" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafieken" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verdeling" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trades" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Uitleg" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -145,6 +146,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>133</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5440680" cy="3337560"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,7 +700,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>9985.01</v>
+        <v>9985.620000000001</v>
       </c>
       <c r="C3" s="2">
         <f>B3-B2</f>
@@ -515,6 +721,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -568,7 +788,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.603</v>
       </c>
     </row>
     <row r="3">
@@ -588,7 +808,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.06</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="4">
@@ -608,18 +828,18 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.06</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -628,18 +848,18 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.06</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -648,18 +868,18 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -668,7 +888,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.06</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="8">
@@ -688,7 +908,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0499</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="9">
@@ -708,7 +928,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.0499</v>
+        <v>0.0501</v>
       </c>
     </row>
     <row r="10">
@@ -717,8 +937,6 @@
           <t>KAS</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" s="3" t="n">
         <v>0</v>
       </c>
@@ -728,7 +946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1080,7 +1298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/rapporten/investeerder.xlsx
+++ b/rapporten/investeerder.xlsx
@@ -534,7 +534,7 @@
         <scaling>
           <orientation val="minMax"/>
           <max val="135"/>
-          <min val="115"/>
+          <min val="110"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9639.620000000001</v>
+        <v>9803.040000000001</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -4046,7 +4046,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>iShares MSCI World (IWDA.AS)  ·  130,18 EUR</t>
+          <t>iShares MSCI World (IWDA.AS)  ·  131,78 EUR</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -4058,7 +4058,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Gestegen: 3,1% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+          <t>Gestegen: 4,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>ASML (ASML.AS)  ·  1.441,00 EUR</t>
+          <t>ASML (ASML.AS)  ·  1.534,80 EUR</t>
         </is>
       </c>
     </row>
@@ -4087,14 +4087,14 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Gedaald: -9,7% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+          <t>Gedaald: -3,9% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Infineon (IFX.DE)  ·  50,53 EUR</t>
+          <t>Infineon (IFX.DE)  ·  55,05 EUR</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -4106,7 +4106,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Gedaald: -21,9% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+          <t>Gedaald: -14,9% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -4118,24 +4118,24 @@
     <row r="69" ht="22" customHeight="1">
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>Ethereum (ETH-USD)  ·  2.376,51 USD</t>
+          <t>Ethereum (ETH-USD)  ·  2.418,21 USD</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>Bitcoin (BTC-USD)  ·  81.413,99 USD</t>
+          <t>Bitcoin (BTC-USD)  ·  81.562,49 USD</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Gestegen: 26,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+          <t>Gestegen: 28,5% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Gestegen: 28,4% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
+          <t>Gestegen: 28,3% in de laatste 3 maanden. Stijgende trend: de koers staat boven beide gemiddelden.</t>
         </is>
       </c>
     </row>
@@ -4200,18 +4200,18 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6148</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ASML.AS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4220,58 +4220,58 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.0595</v>
+        <v>0.0585</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Halfgeleider-ETF</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>STOCK</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.0592</v>
+        <v>0.0585</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Micron</t>
+          <t>Halfgeleider-ETF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>STOCK</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.0572</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASML.AS</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4280,18 +4280,18 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.0559</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Micron</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0533</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="8">
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.0508</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9">
@@ -5244,49 +5244,49 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="AX2" t="n">
+        <v>1871.2637</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1895.7494</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1852.8403</v>
+      </c>
+      <c r="BA2" t="n">
         <v>1881.3735</v>
       </c>
-      <c r="AY2" t="n">
-        <v>1921.7754</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1873.3473</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1878.135</v>
-      </c>
       <c r="BB2" t="n">
-        <v>1812.4882</v>
+        <v>1808.2342</v>
       </c>
       <c r="BC2" t="n">
-        <v>2033.9537</v>
+        <v>2039.3067</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>12 aug</t>
+          <t>11 aug</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>63551.8711</v>
+        <v>63910.1758</v>
       </c>
       <c r="BG2" t="n">
-        <v>64381.0781</v>
+        <v>64433.6797</v>
       </c>
       <c r="BH2" t="n">
-        <v>63251.1133</v>
+        <v>63185.4727</v>
       </c>
       <c r="BI2" t="n">
-        <v>63402.4336</v>
+        <v>63551.875</v>
       </c>
       <c r="BJ2" t="n">
-        <v>63337.5587</v>
+        <v>63322.8705</v>
       </c>
       <c r="BK2" t="n">
-        <v>69743.889</v>
+        <v>69872.4305</v>
       </c>
     </row>
     <row r="3">
@@ -5430,49 +5430,49 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>1878.1885</v>
+        <v>1881.3735</v>
       </c>
       <c r="AY3" t="n">
-        <v>1898.2252</v>
+        <v>1921.7754</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1861.9204</v>
+        <v>1873.3473</v>
       </c>
       <c r="BA3" t="n">
-        <v>1883.9913</v>
+        <v>1878.135</v>
       </c>
       <c r="BB3" t="n">
-        <v>1817.7695</v>
+        <v>1812.4882</v>
       </c>
       <c r="BC3" t="n">
-        <v>2029.2941</v>
+        <v>2033.9537</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>13 aug</t>
+          <t>12 aug</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>63404.4258</v>
+        <v>63551.8711</v>
       </c>
       <c r="BG3" t="n">
-        <v>63926.332</v>
+        <v>64381.0781</v>
       </c>
       <c r="BH3" t="n">
-        <v>62799.2891</v>
+        <v>63251.1133</v>
       </c>
       <c r="BI3" t="n">
-        <v>63402.1719</v>
+        <v>63402.4336</v>
       </c>
       <c r="BJ3" t="n">
-        <v>63385.6995</v>
+        <v>63337.5587</v>
       </c>
       <c r="BK3" t="n">
-        <v>69628.03879999999</v>
+        <v>69743.889</v>
       </c>
     </row>
     <row r="4">
@@ -5616,49 +5616,49 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>1884.017</v>
+        <v>1878.1885</v>
       </c>
       <c r="AY4" t="n">
-        <v>1889.2706</v>
+        <v>1898.2252</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1862.5646</v>
+        <v>1861.9204</v>
       </c>
       <c r="BA4" t="n">
-        <v>1880.65</v>
+        <v>1883.9913</v>
       </c>
       <c r="BB4" t="n">
-        <v>1824.0862</v>
+        <v>1817.7695</v>
       </c>
       <c r="BC4" t="n">
-        <v>2024.0651</v>
+        <v>2029.2941</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>14 aug</t>
+          <t>13 aug</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>63402.0898</v>
+        <v>63404.4258</v>
       </c>
       <c r="BG4" t="n">
-        <v>63551.5625</v>
+        <v>63926.332</v>
       </c>
       <c r="BH4" t="n">
-        <v>62487.6992</v>
+        <v>62799.2891</v>
       </c>
       <c r="BI4" t="n">
-        <v>62975.5938</v>
+        <v>63402.1719</v>
       </c>
       <c r="BJ4" t="n">
-        <v>63450.7779</v>
+        <v>63385.6995</v>
       </c>
       <c r="BK4" t="n">
-        <v>69501.5811</v>
+        <v>69628.03879999999</v>
       </c>
     </row>
     <row r="5">
@@ -5703,7 +5703,7 @@
         <v>865.3239</v>
       </c>
       <c r="N5" t="n">
-        <v>937.4059</v>
+        <v>937.4059999999999</v>
       </c>
       <c r="O5" t="n">
         <v>486.3243</v>
@@ -5802,49 +5802,49 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>1880.613</v>
+        <v>1884.017</v>
       </c>
       <c r="AY5" t="n">
-        <v>1884.718</v>
+        <v>1889.2706</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1874.328</v>
+        <v>1862.5646</v>
       </c>
       <c r="BA5" t="n">
-        <v>1880.9083</v>
+        <v>1880.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>1830.1721</v>
+        <v>1824.0862</v>
       </c>
       <c r="BC5" t="n">
-        <v>2018.3586</v>
+        <v>2024.0651</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>15 aug</t>
+          <t>14 aug</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>62974.3359</v>
+        <v>63402.0898</v>
       </c>
       <c r="BG5" t="n">
-        <v>63119.1328</v>
+        <v>63551.5625</v>
       </c>
       <c r="BH5" t="n">
-        <v>62850.9609</v>
+        <v>62487.6992</v>
       </c>
       <c r="BI5" t="n">
-        <v>63024.3203</v>
+        <v>62975.5938</v>
       </c>
       <c r="BJ5" t="n">
-        <v>63510.9357</v>
+        <v>63450.7779</v>
       </c>
       <c r="BK5" t="n">
-        <v>69371.18979999999</v>
+        <v>69501.5811</v>
       </c>
     </row>
     <row r="6">
@@ -5988,49 +5988,49 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16 aug</t>
+          <t>15 aug</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>1880.8916</v>
+        <v>1880.613</v>
       </c>
       <c r="AY6" t="n">
-        <v>1889.6053</v>
+        <v>1884.718</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1867.8917</v>
+        <v>1874.328</v>
       </c>
       <c r="BA6" t="n">
-        <v>1873.943</v>
+        <v>1880.9083</v>
       </c>
       <c r="BB6" t="n">
-        <v>1836.2191</v>
+        <v>1830.1721</v>
       </c>
       <c r="BC6" t="n">
-        <v>2012.6952</v>
+        <v>2018.3586</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>16 aug</t>
+          <t>15 aug</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>63023.4219</v>
+        <v>62974.3359</v>
       </c>
       <c r="BG6" t="n">
-        <v>63310.7773</v>
+        <v>63119.1328</v>
       </c>
       <c r="BH6" t="n">
-        <v>62648.5742</v>
+        <v>62850.9609</v>
       </c>
       <c r="BI6" t="n">
-        <v>62818.6523</v>
+        <v>63024.3203</v>
       </c>
       <c r="BJ6" t="n">
-        <v>63568.5068</v>
+        <v>63510.9357</v>
       </c>
       <c r="BK6" t="n">
-        <v>69239.3602</v>
+        <v>69371.18979999999</v>
       </c>
     </row>
     <row r="7">
@@ -6075,7 +6075,7 @@
         <v>959.329</v>
       </c>
       <c r="N7" t="n">
-        <v>948.1457</v>
+        <v>948.1458</v>
       </c>
       <c r="O7" t="n">
         <v>494.148</v>
@@ -6174,49 +6174,49 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>16 aug</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>1873.97</v>
+        <v>1880.8916</v>
       </c>
       <c r="AY7" t="n">
-        <v>1916.6569</v>
+        <v>1889.6053</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1870.7479</v>
+        <v>1867.8917</v>
       </c>
       <c r="BA7" t="n">
-        <v>1912.2021</v>
+        <v>1873.943</v>
       </c>
       <c r="BB7" t="n">
-        <v>1843.056</v>
+        <v>1836.2191</v>
       </c>
       <c r="BC7" t="n">
-        <v>2008.1651</v>
+        <v>2012.6952</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>17 aug</t>
+          <t>16 aug</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>62819.3789</v>
+        <v>63023.4219</v>
       </c>
       <c r="BG7" t="n">
-        <v>64547.8477</v>
+        <v>63310.7773</v>
       </c>
       <c r="BH7" t="n">
-        <v>62687.1016</v>
+        <v>62648.5742</v>
       </c>
       <c r="BI7" t="n">
-        <v>64506.2539</v>
+        <v>62818.6523</v>
       </c>
       <c r="BJ7" t="n">
-        <v>63667.9851</v>
+        <v>63568.5068</v>
       </c>
       <c r="BK7" t="n">
-        <v>69139.0836</v>
+        <v>69239.3602</v>
       </c>
     </row>
     <row r="8">
@@ -6360,49 +6360,49 @@
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>1912.2086</v>
+        <v>1873.97</v>
       </c>
       <c r="AY8" t="n">
-        <v>1920.5233</v>
+        <v>1916.6569</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1884.4778</v>
+        <v>1870.7479</v>
       </c>
       <c r="BA8" t="n">
-        <v>1916.4596</v>
+        <v>1912.2021</v>
       </c>
       <c r="BB8" t="n">
-        <v>1849.181</v>
+        <v>1843.056</v>
       </c>
       <c r="BC8" t="n">
-        <v>2004.2355</v>
+        <v>2008.1651</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>18 aug</t>
+          <t>17 aug</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>64506.5234</v>
+        <v>62819.3789</v>
       </c>
       <c r="BG8" t="n">
-        <v>64987.7109</v>
+        <v>64547.8477</v>
       </c>
       <c r="BH8" t="n">
-        <v>63980.3242</v>
+        <v>62687.1016</v>
       </c>
       <c r="BI8" t="n">
-        <v>64680.7109</v>
+        <v>64506.2539</v>
       </c>
       <c r="BJ8" t="n">
-        <v>63758.8317</v>
+        <v>63667.9851</v>
       </c>
       <c r="BK8" t="n">
-        <v>69041.8438</v>
+        <v>69139.0836</v>
       </c>
     </row>
     <row r="9">
@@ -6447,7 +6447,7 @@
         <v>920.8051</v>
       </c>
       <c r="N9" t="n">
-        <v>955.1344</v>
+        <v>955.1345</v>
       </c>
       <c r="O9" t="n">
         <v>501.8105</v>
@@ -6546,49 +6546,49 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>1916.4268</v>
+        <v>1912.2086</v>
       </c>
       <c r="AY9" t="n">
-        <v>2327.7012</v>
+        <v>1920.5233</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1905.0824</v>
+        <v>1884.4778</v>
       </c>
       <c r="BA9" t="n">
-        <v>2251.458</v>
+        <v>1916.4596</v>
       </c>
       <c r="BB9" t="n">
-        <v>1862.8185</v>
+        <v>1849.181</v>
       </c>
       <c r="BC9" t="n">
-        <v>2003.2673</v>
+        <v>2004.2355</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>19 aug</t>
+          <t>18 aug</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>64680.0469</v>
+        <v>64506.5234</v>
       </c>
       <c r="BG9" t="n">
-        <v>69996.9531</v>
+        <v>64987.7109</v>
       </c>
       <c r="BH9" t="n">
-        <v>64111.0703</v>
+        <v>63980.3242</v>
       </c>
       <c r="BI9" t="n">
-        <v>69266.1875</v>
+        <v>64680.7109</v>
       </c>
       <c r="BJ9" t="n">
-        <v>63972.9783</v>
+        <v>63758.8317</v>
       </c>
       <c r="BK9" t="n">
-        <v>68995.0692</v>
+        <v>69041.8438</v>
       </c>
     </row>
     <row r="10">
@@ -6732,49 +6732,49 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>2251.4441</v>
+        <v>1916.4268</v>
       </c>
       <c r="AY10" t="n">
-        <v>2357.2283</v>
+        <v>2327.7012</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2222.5747</v>
+        <v>1905.0824</v>
       </c>
       <c r="BA10" t="n">
-        <v>2326.3848</v>
+        <v>2251.458</v>
       </c>
       <c r="BB10" t="n">
-        <v>1877.167</v>
+        <v>1862.8185</v>
       </c>
       <c r="BC10" t="n">
-        <v>2003.5594</v>
+        <v>2003.2673</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>20 aug</t>
+          <t>19 aug</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>69268.25</v>
+        <v>64680.0469</v>
       </c>
       <c r="BG10" t="n">
-        <v>73369.80469999999</v>
+        <v>69996.9531</v>
       </c>
       <c r="BH10" t="n">
-        <v>68867.5312</v>
+        <v>64111.0703</v>
       </c>
       <c r="BI10" t="n">
-        <v>73032.75780000001</v>
+        <v>69266.1875</v>
       </c>
       <c r="BJ10" t="n">
-        <v>64233.5583</v>
+        <v>63972.9783</v>
       </c>
       <c r="BK10" t="n">
-        <v>68975.36079999999</v>
+        <v>68995.0692</v>
       </c>
     </row>
     <row r="11">
@@ -6918,49 +6918,49 @@
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>2326.3823</v>
+        <v>2251.4441</v>
       </c>
       <c r="AY11" t="n">
-        <v>2545.8811</v>
+        <v>2357.2283</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2324.7095</v>
+        <v>2222.5747</v>
       </c>
       <c r="BA11" t="n">
-        <v>2515.2817</v>
+        <v>2326.3848</v>
       </c>
       <c r="BB11" t="n">
-        <v>1893.5093</v>
+        <v>1877.167</v>
       </c>
       <c r="BC11" t="n">
-        <v>2004.4141</v>
+        <v>2003.5594</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>21 aug</t>
+          <t>20 aug</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>73031.08590000001</v>
+        <v>69268.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>79463.71090000001</v>
+        <v>73369.80469999999</v>
       </c>
       <c r="BH11" t="n">
-        <v>73011.41409999999</v>
+        <v>68867.5312</v>
       </c>
       <c r="BI11" t="n">
-        <v>78335.1875</v>
+        <v>73032.75780000001</v>
       </c>
       <c r="BJ11" t="n">
-        <v>64570.556</v>
+        <v>64233.5583</v>
       </c>
       <c r="BK11" t="n">
-        <v>68973.5929</v>
+        <v>68975.36079999999</v>
       </c>
     </row>
     <row r="12">
@@ -7005,7 +7005,7 @@
         <v>738.8837</v>
       </c>
       <c r="N12" t="n">
-        <v>958.2496</v>
+        <v>958.2497</v>
       </c>
       <c r="O12" t="n">
         <v>511.2377</v>
@@ -7054,7 +7054,7 @@
         <v>1535.0628</v>
       </c>
       <c r="AE12" t="n">
-        <v>1201.4255</v>
+        <v>1201.4256</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -7104,49 +7104,49 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>22 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>2515.3923</v>
+        <v>2326.3823</v>
       </c>
       <c r="AY12" t="n">
-        <v>2528.8967</v>
+        <v>2545.8811</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2389.9021</v>
+        <v>2324.7095</v>
       </c>
       <c r="BA12" t="n">
-        <v>2424.2512</v>
+        <v>2515.2817</v>
       </c>
       <c r="BB12" t="n">
-        <v>1906.8639</v>
+        <v>1893.5093</v>
       </c>
       <c r="BC12" t="n">
-        <v>2005.3975</v>
+        <v>2004.4141</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>22 aug</t>
+          <t>21 aug</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>78332.55469999999</v>
+        <v>73031.08590000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>78801.14840000001</v>
+        <v>79463.71090000001</v>
       </c>
       <c r="BH12" t="n">
-        <v>76526.71090000001</v>
+        <v>73011.41409999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>77083.41409999999</v>
+        <v>78335.1875</v>
       </c>
       <c r="BJ12" t="n">
-        <v>64861.3403</v>
+        <v>64570.556</v>
       </c>
       <c r="BK12" t="n">
-        <v>68980.8422</v>
+        <v>68973.5929</v>
       </c>
     </row>
     <row r="13">
@@ -7240,7 +7240,7 @@
         <v>1535.6006</v>
       </c>
       <c r="AE13" t="n">
-        <v>1204.238</v>
+        <v>1204.2381</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -7290,49 +7290,49 @@
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>23 aug</t>
+          <t>22 aug</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>2424.217</v>
+        <v>2515.3923</v>
       </c>
       <c r="AY13" t="n">
-        <v>2483.9304</v>
+        <v>2528.8967</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2357.1399</v>
+        <v>2389.9021</v>
       </c>
       <c r="BA13" t="n">
-        <v>2463.8159</v>
+        <v>2424.2512</v>
       </c>
       <c r="BB13" t="n">
-        <v>1920.5596</v>
+        <v>1906.8639</v>
       </c>
       <c r="BC13" t="n">
-        <v>2006.9991</v>
+        <v>2005.3975</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>23 aug</t>
+          <t>22 aug</t>
         </is>
       </c>
       <c r="BF13" t="n">
-        <v>77082.8438</v>
+        <v>78332.55469999999</v>
       </c>
       <c r="BG13" t="n">
-        <v>78036.86719999999</v>
+        <v>78801.14840000001</v>
       </c>
       <c r="BH13" t="n">
-        <v>75624.94530000001</v>
+        <v>76526.71090000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>77755.2656</v>
+        <v>77083.41409999999</v>
       </c>
       <c r="BJ13" t="n">
-        <v>65154.6795</v>
+        <v>64861.3403</v>
       </c>
       <c r="BK13" t="n">
-        <v>69004.52</v>
+        <v>68980.8422</v>
       </c>
     </row>
     <row r="14">
@@ -7476,49 +7476,49 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>23 aug</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>2463.6406</v>
+        <v>2424.217</v>
       </c>
       <c r="AY14" t="n">
-        <v>2531.7449</v>
+        <v>2483.9304</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2425.3879</v>
+        <v>2357.1399</v>
       </c>
       <c r="BA14" t="n">
-        <v>2481.8313</v>
+        <v>2463.8159</v>
       </c>
       <c r="BB14" t="n">
-        <v>1934.5361</v>
+        <v>1920.5596</v>
       </c>
       <c r="BC14" t="n">
-        <v>2010.2998</v>
+        <v>2006.9991</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>24 aug</t>
+          <t>23 aug</t>
         </is>
       </c>
       <c r="BF14" t="n">
-        <v>77748.875</v>
+        <v>77082.8438</v>
       </c>
       <c r="BG14" t="n">
-        <v>79970.1094</v>
+        <v>78036.86719999999</v>
       </c>
       <c r="BH14" t="n">
-        <v>76688.8281</v>
+        <v>75624.94530000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>78964.4844</v>
+        <v>77755.2656</v>
       </c>
       <c r="BJ14" t="n">
-        <v>65463.0116</v>
+        <v>65154.6795</v>
       </c>
       <c r="BK14" t="n">
-        <v>69085.83199999999</v>
+        <v>69004.52</v>
       </c>
     </row>
     <row r="15">
@@ -7662,49 +7662,49 @@
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>2481.7778</v>
+        <v>2463.6406</v>
       </c>
       <c r="AY15" t="n">
-        <v>2531.0845</v>
+        <v>2531.7449</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2416.6028</v>
+        <v>2425.3879</v>
       </c>
       <c r="BA15" t="n">
-        <v>2443.1594</v>
+        <v>2481.8313</v>
       </c>
       <c r="BB15" t="n">
-        <v>1947.4478</v>
+        <v>1934.5361</v>
       </c>
       <c r="BC15" t="n">
-        <v>2012.1987</v>
+        <v>2010.2998</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>25 aug</t>
+          <t>24 aug</t>
         </is>
       </c>
       <c r="BF15" t="n">
-        <v>78960.0938</v>
+        <v>77748.875</v>
       </c>
       <c r="BG15" t="n">
-        <v>81235.0312</v>
+        <v>79970.1094</v>
       </c>
       <c r="BH15" t="n">
-        <v>77870.625</v>
+        <v>76688.8281</v>
       </c>
       <c r="BI15" t="n">
-        <v>78564.97659999999</v>
+        <v>78964.4844</v>
       </c>
       <c r="BJ15" t="n">
-        <v>65754.4108</v>
+        <v>65463.0116</v>
       </c>
       <c r="BK15" t="n">
-        <v>69125.8799</v>
+        <v>69085.83199999999</v>
       </c>
     </row>
     <row r="16">
@@ -7848,49 +7848,49 @@
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>2442.4893</v>
+        <v>2481.7778</v>
       </c>
       <c r="AY16" t="n">
-        <v>2514.6663</v>
+        <v>2531.0845</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2432.5122</v>
+        <v>2416.6028</v>
       </c>
       <c r="BA16" t="n">
-        <v>2506.261</v>
+        <v>2443.1594</v>
       </c>
       <c r="BB16" t="n">
-        <v>1962.2028</v>
+        <v>1947.4478</v>
       </c>
       <c r="BC16" t="n">
-        <v>2014.2773</v>
+        <v>2012.1987</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>26 aug</t>
+          <t>25 aug</t>
         </is>
       </c>
       <c r="BF16" t="n">
-        <v>78538.58590000001</v>
+        <v>78960.0938</v>
       </c>
       <c r="BG16" t="n">
-        <v>79240.5</v>
+        <v>81235.0312</v>
       </c>
       <c r="BH16" t="n">
-        <v>77639.83590000001</v>
+        <v>77870.625</v>
       </c>
       <c r="BI16" t="n">
-        <v>79027.4219</v>
+        <v>78564.97659999999</v>
       </c>
       <c r="BJ16" t="n">
-        <v>66069.0113</v>
+        <v>65754.4108</v>
       </c>
       <c r="BK16" t="n">
-        <v>69174.60709999999</v>
+        <v>69125.8799</v>
       </c>
     </row>
     <row r="17">
@@ -7984,7 +7984,7 @@
         <v>1541.0191</v>
       </c>
       <c r="AE17" t="n">
-        <v>1215.9398</v>
+        <v>1215.9399</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -8034,49 +8034,49 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>2506.2395</v>
+        <v>2442.4893</v>
       </c>
       <c r="AY17" t="n">
-        <v>2564.2744</v>
+        <v>2514.6663</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2481.9448</v>
+        <v>2432.5122</v>
       </c>
       <c r="BA17" t="n">
-        <v>2510.4102</v>
+        <v>2506.261</v>
       </c>
       <c r="BB17" t="n">
-        <v>1977.5574</v>
+        <v>1962.2028</v>
       </c>
       <c r="BC17" t="n">
-        <v>2016.3855</v>
+        <v>2014.2773</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>27 aug</t>
+          <t>26 aug</t>
         </is>
       </c>
       <c r="BF17" t="n">
-        <v>79037.9219</v>
+        <v>78538.58590000001</v>
       </c>
       <c r="BG17" t="n">
-        <v>80806.5625</v>
+        <v>79240.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>78591.10159999999</v>
+        <v>77639.83590000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>80257.53909999999</v>
+        <v>79027.4219</v>
       </c>
       <c r="BJ17" t="n">
-        <v>66429.01059999999</v>
+        <v>66069.0113</v>
       </c>
       <c r="BK17" t="n">
-        <v>69224.57120000001</v>
+        <v>69174.60709999999</v>
       </c>
     </row>
     <row r="18">
@@ -8220,49 +8220,49 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>2510.6726</v>
+        <v>2506.2395</v>
       </c>
       <c r="AY18" t="n">
-        <v>2534.0122</v>
+        <v>2564.2744</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2408.7234</v>
+        <v>2481.9448</v>
       </c>
       <c r="BA18" t="n">
-        <v>2442.5359</v>
+        <v>2510.4102</v>
       </c>
       <c r="BB18" t="n">
-        <v>1991.5184</v>
+        <v>1977.5574</v>
       </c>
       <c r="BC18" t="n">
-        <v>2018.0803</v>
+        <v>2016.3855</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>28 aug</t>
+          <t>27 aug</t>
         </is>
       </c>
       <c r="BF18" t="n">
-        <v>80264.64840000001</v>
+        <v>79037.9219</v>
       </c>
       <c r="BG18" t="n">
-        <v>81346.9531</v>
+        <v>80806.5625</v>
       </c>
       <c r="BH18" t="n">
-        <v>76909.35159999999</v>
+        <v>78591.10159999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>77830.28909999999</v>
+        <v>80257.53909999999</v>
       </c>
       <c r="BJ18" t="n">
-        <v>66721.7534</v>
+        <v>66429.01059999999</v>
       </c>
       <c r="BK18" t="n">
-        <v>69263.11870000001</v>
+        <v>69224.57120000001</v>
       </c>
     </row>
     <row r="19">
@@ -8307,7 +8307,7 @@
         <v>877.4319</v>
       </c>
       <c r="N19" t="n">
-        <v>970.713</v>
+        <v>970.7131000000001</v>
       </c>
       <c r="O19" t="n">
         <v>534.7758</v>
@@ -8406,49 +8406,49 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>29 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>2442.5647</v>
+        <v>2510.6726</v>
       </c>
       <c r="AY19" t="n">
-        <v>2459.6292</v>
+        <v>2534.0122</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2430.811</v>
+        <v>2408.7234</v>
       </c>
       <c r="BA19" t="n">
-        <v>2457.6863</v>
+        <v>2442.5359</v>
       </c>
       <c r="BB19" t="n">
-        <v>2004.7583</v>
+        <v>1991.5184</v>
       </c>
       <c r="BC19" t="n">
-        <v>2020.2713</v>
+        <v>2018.0803</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>29 aug</t>
+          <t>28 aug</t>
         </is>
       </c>
       <c r="BF19" t="n">
-        <v>77830.8906</v>
+        <v>80264.64840000001</v>
       </c>
       <c r="BG19" t="n">
-        <v>78327.94530000001</v>
+        <v>81346.9531</v>
       </c>
       <c r="BH19" t="n">
-        <v>77381.89840000001</v>
+        <v>76909.35159999999</v>
       </c>
       <c r="BI19" t="n">
-        <v>78245.8125</v>
+        <v>77830.28909999999</v>
       </c>
       <c r="BJ19" t="n">
-        <v>67004.1269</v>
+        <v>66721.7534</v>
       </c>
       <c r="BK19" t="n">
-        <v>69310.378</v>
+        <v>69263.11870000001</v>
       </c>
     </row>
     <row r="20">
@@ -8592,49 +8592,49 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>30 aug</t>
+          <t>29 aug</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>2457.6919</v>
+        <v>2442.5647</v>
       </c>
       <c r="AY20" t="n">
-        <v>2532.959</v>
+        <v>2459.6292</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2389.4692</v>
+        <v>2430.811</v>
       </c>
       <c r="BA20" t="n">
-        <v>2417.9387</v>
+        <v>2457.6863</v>
       </c>
       <c r="BB20" t="n">
-        <v>2017.3551</v>
+        <v>2004.7583</v>
       </c>
       <c r="BC20" t="n">
-        <v>2022.6579</v>
+        <v>2020.2713</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>30 aug</t>
+          <t>29 aug</t>
         </is>
       </c>
       <c r="BF20" t="n">
-        <v>78246.1719</v>
+        <v>77830.8906</v>
       </c>
       <c r="BG20" t="n">
-        <v>79373.17969999999</v>
+        <v>78327.94530000001</v>
       </c>
       <c r="BH20" t="n">
-        <v>77056.14840000001</v>
+        <v>77381.89840000001</v>
       </c>
       <c r="BI20" t="n">
-        <v>77667.57030000001</v>
+        <v>78245.8125</v>
       </c>
       <c r="BJ20" t="n">
-        <v>67281.43769999999</v>
+        <v>67004.1269</v>
       </c>
       <c r="BK20" t="n">
-        <v>69363.75599999999</v>
+        <v>69310.378</v>
       </c>
     </row>
     <row r="21">
@@ -8778,49 +8778,49 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>30 aug</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>2417.9031</v>
+        <v>2457.6919</v>
       </c>
       <c r="AY21" t="n">
-        <v>2488.9229</v>
+        <v>2532.959</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2401.8088</v>
+        <v>2389.4692</v>
       </c>
       <c r="BA21" t="n">
-        <v>2466.8203</v>
+        <v>2417.9387</v>
       </c>
       <c r="BB21" t="n">
-        <v>2030.5757</v>
+        <v>2017.3551</v>
       </c>
       <c r="BC21" t="n">
-        <v>2025.2573</v>
+        <v>2022.6579</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>31 aug</t>
+          <t>30 aug</t>
         </is>
       </c>
       <c r="BF21" t="n">
-        <v>77673.7031</v>
+        <v>78246.1719</v>
       </c>
       <c r="BG21" t="n">
-        <v>79247.3438</v>
+        <v>79373.17969999999</v>
       </c>
       <c r="BH21" t="n">
-        <v>77378.4375</v>
+        <v>77056.14840000001</v>
       </c>
       <c r="BI21" t="n">
-        <v>78548.63280000001</v>
+        <v>77667.57030000001</v>
       </c>
       <c r="BJ21" t="n">
-        <v>67577.246</v>
+        <v>67281.43769999999</v>
       </c>
       <c r="BK21" t="n">
-        <v>69425.39</v>
+        <v>69363.75599999999</v>
       </c>
     </row>
     <row r="22">
@@ -8964,49 +8964,49 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>2466.5752</v>
+        <v>2417.9031</v>
       </c>
       <c r="AY22" t="n">
-        <v>2484.3989</v>
+        <v>2488.9229</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2383.8037</v>
+        <v>2401.8088</v>
       </c>
       <c r="BA22" t="n">
-        <v>2417.842</v>
+        <v>2466.8203</v>
       </c>
       <c r="BB22" t="n">
-        <v>2043.4626</v>
+        <v>2030.5757</v>
       </c>
       <c r="BC22" t="n">
-        <v>2027.1038</v>
+        <v>2025.2573</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>1 sep</t>
+          <t>31 aug</t>
         </is>
       </c>
       <c r="BF22" t="n">
-        <v>78539.8594</v>
+        <v>77673.7031</v>
       </c>
       <c r="BG22" t="n">
-        <v>79196.5156</v>
+        <v>79247.3438</v>
       </c>
       <c r="BH22" t="n">
-        <v>76399.0625</v>
+        <v>77378.4375</v>
       </c>
       <c r="BI22" t="n">
-        <v>77403.625</v>
+        <v>78548.63280000001</v>
       </c>
       <c r="BJ22" t="n">
-        <v>67880.5361</v>
+        <v>67577.246</v>
       </c>
       <c r="BK22" t="n">
-        <v>69468.1189</v>
+        <v>69425.39</v>
       </c>
     </row>
     <row r="23">
@@ -9150,49 +9150,49 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>2417.8284</v>
+        <v>2466.5752</v>
       </c>
       <c r="AY23" t="n">
-        <v>2427.4016</v>
+        <v>2484.3989</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2356.1882</v>
+        <v>2383.8037</v>
       </c>
       <c r="BA23" t="n">
-        <v>2391.501</v>
+        <v>2417.842</v>
       </c>
       <c r="BB23" t="n">
-        <v>2053.503</v>
+        <v>2043.4626</v>
       </c>
       <c r="BC23" t="n">
-        <v>2028.6313</v>
+        <v>2027.1038</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>2 sep</t>
+          <t>1 sep</t>
         </is>
       </c>
       <c r="BF23" t="n">
-        <v>77402.1406</v>
+        <v>78539.8594</v>
       </c>
       <c r="BG23" t="n">
-        <v>77737.5469</v>
+        <v>79196.5156</v>
       </c>
       <c r="BH23" t="n">
-        <v>76248.30469999999</v>
+        <v>76399.0625</v>
       </c>
       <c r="BI23" t="n">
-        <v>77300.47659999999</v>
+        <v>77403.625</v>
       </c>
       <c r="BJ23" t="n">
-        <v>68127.4234</v>
+        <v>67880.5361</v>
       </c>
       <c r="BK23" t="n">
-        <v>69505.7831</v>
+        <v>69468.1189</v>
       </c>
     </row>
     <row r="24">
@@ -9336,49 +9336,49 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>2391.5999</v>
+        <v>2417.8284</v>
       </c>
       <c r="AY24" t="n">
-        <v>2526.9502</v>
+        <v>2427.4016</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2370.4155</v>
+        <v>2356.1882</v>
       </c>
       <c r="BA24" t="n">
-        <v>2508.0208</v>
+        <v>2391.501</v>
       </c>
       <c r="BB24" t="n">
-        <v>2065.3245</v>
+        <v>2053.503</v>
       </c>
       <c r="BC24" t="n">
-        <v>2031.3412</v>
+        <v>2028.6313</v>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>3 sep</t>
+          <t>2 sep</t>
         </is>
       </c>
       <c r="BF24" t="n">
-        <v>77300.16409999999</v>
+        <v>77402.1406</v>
       </c>
       <c r="BG24" t="n">
-        <v>82262.21090000001</v>
+        <v>77737.5469</v>
       </c>
       <c r="BH24" t="n">
-        <v>76940.88280000001</v>
+        <v>76248.30469999999</v>
       </c>
       <c r="BI24" t="n">
-        <v>81271.74219999999</v>
+        <v>77300.47659999999</v>
       </c>
       <c r="BJ24" t="n">
-        <v>68458.6107</v>
+        <v>68127.4234</v>
       </c>
       <c r="BK24" t="n">
-        <v>69568.2009</v>
+        <v>69505.7831</v>
       </c>
     </row>
     <row r="25">
@@ -9522,49 +9522,49 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>2508.0159</v>
+        <v>2391.5999</v>
       </c>
       <c r="AY25" t="n">
-        <v>2545.6235</v>
+        <v>2526.9502</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2432.3542</v>
+        <v>2370.4155</v>
       </c>
       <c r="BA25" t="n">
-        <v>2456.0781</v>
+        <v>2508.0208</v>
       </c>
       <c r="BB25" t="n">
-        <v>2077.1822</v>
+        <v>2065.3245</v>
       </c>
       <c r="BC25" t="n">
-        <v>2033.632</v>
+        <v>2031.3412</v>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>4 sep</t>
+          <t>3 sep</t>
         </is>
       </c>
       <c r="BF25" t="n">
-        <v>81271.53909999999</v>
+        <v>77300.16409999999</v>
       </c>
       <c r="BG25" t="n">
-        <v>81433.14840000001</v>
+        <v>82262.21090000001</v>
       </c>
       <c r="BH25" t="n">
-        <v>78641.625</v>
+        <v>76940.88280000001</v>
       </c>
       <c r="BI25" t="n">
-        <v>79671.9688</v>
+        <v>81271.74219999999</v>
       </c>
       <c r="BJ25" t="n">
-        <v>68776.2645</v>
+        <v>68458.6107</v>
       </c>
       <c r="BK25" t="n">
-        <v>69622.345</v>
+        <v>69568.2009</v>
       </c>
     </row>
     <row r="26">
@@ -9708,49 +9708,49 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>5 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>2455.988</v>
+        <v>2508.0159</v>
       </c>
       <c r="AY26" t="n">
-        <v>2492.0056</v>
+        <v>2545.6235</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2445.6858</v>
+        <v>2432.3542</v>
       </c>
       <c r="BA26" t="n">
-        <v>2480.7356</v>
+        <v>2456.0781</v>
       </c>
       <c r="BB26" t="n">
-        <v>2089.9772</v>
+        <v>2077.1822</v>
       </c>
       <c r="BC26" t="n">
-        <v>2036.0747</v>
+        <v>2033.632</v>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>5 sep</t>
+          <t>4 sep</t>
         </is>
       </c>
       <c r="BF26" t="n">
-        <v>79671.7031</v>
+        <v>81271.53909999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>80194.50780000001</v>
+        <v>81433.14840000001</v>
       </c>
       <c r="BH26" t="n">
-        <v>79465.0625</v>
+        <v>78641.625</v>
       </c>
       <c r="BI26" t="n">
-        <v>79823.86719999999</v>
+        <v>79671.9688</v>
       </c>
       <c r="BJ26" t="n">
-        <v>69094.75260000001</v>
+        <v>68776.2645</v>
       </c>
       <c r="BK26" t="n">
-        <v>69683.9932</v>
+        <v>69622.345</v>
       </c>
     </row>
     <row r="27">
@@ -9795,7 +9795,7 @@
         <v>936.9625</v>
       </c>
       <c r="N27" t="n">
-        <v>962.1174</v>
+        <v>962.1174999999999</v>
       </c>
       <c r="O27" t="n">
         <v>563.4435999999999</v>
@@ -9894,49 +9894,49 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>6 sep</t>
+          <t>5 sep</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>2480.8247</v>
+        <v>2455.988</v>
       </c>
       <c r="AY27" t="n">
-        <v>2525.3215</v>
+        <v>2492.0056</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2468.1948</v>
+        <v>2445.6858</v>
       </c>
       <c r="BA27" t="n">
-        <v>2514.5488</v>
+        <v>2480.7356</v>
       </c>
       <c r="BB27" t="n">
-        <v>2103.0403</v>
+        <v>2089.9772</v>
       </c>
       <c r="BC27" t="n">
-        <v>2038.8776</v>
+        <v>2036.0747</v>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>6 sep</t>
+          <t>5 sep</t>
         </is>
       </c>
       <c r="BF27" t="n">
-        <v>79824.60159999999</v>
+        <v>79671.7031</v>
       </c>
       <c r="BG27" t="n">
-        <v>80530.64840000001</v>
+        <v>80194.50780000001</v>
       </c>
       <c r="BH27" t="n">
-        <v>79327.5</v>
+        <v>79465.0625</v>
       </c>
       <c r="BI27" t="n">
-        <v>80350.0469</v>
+        <v>79823.86719999999</v>
       </c>
       <c r="BJ27" t="n">
-        <v>69405.82150000001</v>
+        <v>69094.75260000001</v>
       </c>
       <c r="BK27" t="n">
-        <v>69753.6168</v>
+        <v>69683.9932</v>
       </c>
     </row>
     <row r="28">
@@ -10080,49 +10080,49 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>6 sep</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>2514.583</v>
+        <v>2480.8247</v>
       </c>
       <c r="AY28" t="n">
-        <v>2534.8618</v>
+        <v>2525.3215</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2466.9131</v>
+        <v>2468.1948</v>
       </c>
       <c r="BA28" t="n">
-        <v>2490.958</v>
+        <v>2514.5488</v>
       </c>
       <c r="BB28" t="n">
-        <v>2115.4293</v>
+        <v>2103.0403</v>
       </c>
       <c r="BC28" t="n">
-        <v>2041.5913</v>
+        <v>2038.8776</v>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>7 sep</t>
+          <t>6 sep</t>
         </is>
       </c>
       <c r="BF28" t="n">
-        <v>80349.19530000001</v>
+        <v>79824.60159999999</v>
       </c>
       <c r="BG28" t="n">
-        <v>80432.3125</v>
+        <v>80530.64840000001</v>
       </c>
       <c r="BH28" t="n">
-        <v>78684.92969999999</v>
+        <v>79327.5</v>
       </c>
       <c r="BI28" t="n">
-        <v>79115.85159999999</v>
+        <v>80350.0469</v>
       </c>
       <c r="BJ28" t="n">
-        <v>69694.3224</v>
+        <v>69405.82150000001</v>
       </c>
       <c r="BK28" t="n">
-        <v>69814.40850000001</v>
+        <v>69753.6168</v>
       </c>
     </row>
     <row r="29">
@@ -10266,49 +10266,49 @@
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>2490.9197</v>
+        <v>2514.583</v>
       </c>
       <c r="AY29" t="n">
-        <v>2506.7532</v>
+        <v>2534.8618</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2441.3289</v>
+        <v>2466.9131</v>
       </c>
       <c r="BA29" t="n">
-        <v>2484.9414</v>
+        <v>2490.958</v>
       </c>
       <c r="BB29" t="n">
-        <v>2127.0529</v>
+        <v>2115.4293</v>
       </c>
       <c r="BC29" t="n">
-        <v>2044.1709</v>
+        <v>2041.5913</v>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>8 sep</t>
+          <t>7 sep</t>
         </is>
       </c>
       <c r="BF29" t="n">
-        <v>79114.9062</v>
+        <v>80349.19530000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>79463.27340000001</v>
+        <v>80432.3125</v>
       </c>
       <c r="BH29" t="n">
-        <v>77635.6875</v>
+        <v>78684.92969999999</v>
       </c>
       <c r="BI29" t="n">
-        <v>78438.5781</v>
+        <v>79115.85159999999</v>
       </c>
       <c r="BJ29" t="n">
-        <v>69958.49340000001</v>
+        <v>69694.3224</v>
       </c>
       <c r="BK29" t="n">
-        <v>69866.57429999999</v>
+        <v>69814.40850000001</v>
       </c>
     </row>
     <row r="30">
@@ -10452,49 +10452,49 @@
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>2484.8943</v>
+        <v>2490.9197</v>
       </c>
       <c r="AY30" t="n">
-        <v>2522.3696</v>
+        <v>2506.7532</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2443.7024</v>
+        <v>2441.3289</v>
       </c>
       <c r="BA30" t="n">
-        <v>2466.9138</v>
+        <v>2484.9414</v>
       </c>
       <c r="BB30" t="n">
-        <v>2137.8235</v>
+        <v>2127.0529</v>
       </c>
       <c r="BC30" t="n">
-        <v>2046.6368</v>
+        <v>2044.1709</v>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>9 sep</t>
+          <t>8 sep</t>
         </is>
       </c>
       <c r="BF30" t="n">
-        <v>78440.60159999999</v>
+        <v>79114.9062</v>
       </c>
       <c r="BG30" t="n">
-        <v>79737.2969</v>
+        <v>79463.27340000001</v>
       </c>
       <c r="BH30" t="n">
-        <v>77768.14840000001</v>
+        <v>77635.6875</v>
       </c>
       <c r="BI30" t="n">
-        <v>78259.52340000001</v>
+        <v>78438.5781</v>
       </c>
       <c r="BJ30" t="n">
-        <v>70193.5814</v>
+        <v>69958.49340000001</v>
       </c>
       <c r="BK30" t="n">
-        <v>69917.853</v>
+        <v>69866.57429999999</v>
       </c>
     </row>
     <row r="31">
@@ -10638,49 +10638,49 @@
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>2466.9131</v>
+        <v>2484.8943</v>
       </c>
       <c r="AY31" t="n">
-        <v>2483.72</v>
+        <v>2522.3696</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2406.9065</v>
+        <v>2443.7024</v>
       </c>
       <c r="BA31" t="n">
-        <v>2437.0986</v>
+        <v>2466.9138</v>
       </c>
       <c r="BB31" t="n">
-        <v>2147.8957</v>
+        <v>2137.8235</v>
       </c>
       <c r="BC31" t="n">
-        <v>2049.0333</v>
+        <v>2046.6368</v>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>10 sep</t>
+          <t>9 sep</t>
         </is>
       </c>
       <c r="BF31" t="n">
-        <v>78260.38280000001</v>
+        <v>78440.60159999999</v>
       </c>
       <c r="BG31" t="n">
-        <v>78520.9688</v>
+        <v>79737.2969</v>
       </c>
       <c r="BH31" t="n">
-        <v>76470.6406</v>
+        <v>77768.14840000001</v>
       </c>
       <c r="BI31" t="n">
-        <v>76568.125</v>
+        <v>78259.52340000001</v>
       </c>
       <c r="BJ31" t="n">
-        <v>70402.928</v>
+        <v>70193.5814</v>
       </c>
       <c r="BK31" t="n">
-        <v>69962.3967</v>
+        <v>69917.853</v>
       </c>
     </row>
     <row r="32">
@@ -10824,49 +10824,49 @@
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>2437.1357</v>
+        <v>2466.9131</v>
       </c>
       <c r="AY32" t="n">
-        <v>2663.0503</v>
+        <v>2483.72</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2435.2854</v>
+        <v>2406.9065</v>
       </c>
       <c r="BA32" t="n">
-        <v>2514.7339</v>
+        <v>2437.0986</v>
       </c>
       <c r="BB32" t="n">
-        <v>2160.6484</v>
+        <v>2147.8957</v>
       </c>
       <c r="BC32" t="n">
-        <v>2052.3294</v>
+        <v>2049.0333</v>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>11 sep</t>
+          <t>10 sep</t>
         </is>
       </c>
       <c r="BF32" t="n">
-        <v>76559.125</v>
+        <v>78260.38280000001</v>
       </c>
       <c r="BG32" t="n">
-        <v>79818.33590000001</v>
+        <v>78520.9688</v>
       </c>
       <c r="BH32" t="n">
-        <v>76162.91409999999</v>
+        <v>76470.6406</v>
       </c>
       <c r="BI32" t="n">
-        <v>77173.7969</v>
+        <v>76568.125</v>
       </c>
       <c r="BJ32" t="n">
-        <v>70645.5077</v>
+        <v>70402.928</v>
       </c>
       <c r="BK32" t="n">
-        <v>70025.182</v>
+        <v>69962.3967</v>
       </c>
     </row>
     <row r="33">
@@ -11010,49 +11010,49 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>12 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>2514.77</v>
+        <v>2437.1357</v>
       </c>
       <c r="AY33" t="n">
-        <v>2544.4724</v>
+        <v>2663.0503</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2508.8015</v>
+        <v>2435.2854</v>
       </c>
       <c r="BA33" t="n">
-        <v>2525.9446</v>
+        <v>2514.7339</v>
       </c>
       <c r="BB33" t="n">
-        <v>2173.9637</v>
+        <v>2160.6484</v>
       </c>
       <c r="BC33" t="n">
-        <v>2055.6943</v>
+        <v>2052.3294</v>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>12 sep</t>
+          <t>11 sep</t>
         </is>
       </c>
       <c r="BF33" t="n">
-        <v>77175.07030000001</v>
+        <v>76559.125</v>
       </c>
       <c r="BG33" t="n">
-        <v>77479.6562</v>
+        <v>79818.33590000001</v>
       </c>
       <c r="BH33" t="n">
-        <v>77045</v>
+        <v>76162.91409999999</v>
       </c>
       <c r="BI33" t="n">
-        <v>77270.4688</v>
+        <v>77173.7969</v>
       </c>
       <c r="BJ33" t="n">
-        <v>70908.9471</v>
+        <v>70645.5077</v>
       </c>
       <c r="BK33" t="n">
-        <v>70091.1341</v>
+        <v>70025.182</v>
       </c>
     </row>
     <row r="34">
@@ -11196,49 +11196,49 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>13 sep</t>
+          <t>12 sep</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>2525.9424</v>
+        <v>2514.77</v>
       </c>
       <c r="AY34" t="n">
-        <v>2526.8538</v>
+        <v>2544.4724</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2462.8396</v>
+        <v>2508.8015</v>
       </c>
       <c r="BA34" t="n">
-        <v>2477.0208</v>
+        <v>2525.9446</v>
       </c>
       <c r="BB34" t="n">
-        <v>2186.0397</v>
+        <v>2173.9637</v>
       </c>
       <c r="BC34" t="n">
-        <v>2057.8063</v>
+        <v>2055.6943</v>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>13 sep</t>
+          <t>12 sep</t>
         </is>
       </c>
       <c r="BF34" t="n">
-        <v>77270.17969999999</v>
+        <v>77175.07030000001</v>
       </c>
       <c r="BG34" t="n">
-        <v>77415.6562</v>
+        <v>77479.6562</v>
       </c>
       <c r="BH34" t="n">
-        <v>76498.38280000001</v>
+        <v>77045</v>
       </c>
       <c r="BI34" t="n">
-        <v>76838.1562</v>
+        <v>77270.4688</v>
       </c>
       <c r="BJ34" t="n">
-        <v>71159.474</v>
+        <v>70908.9471</v>
       </c>
       <c r="BK34" t="n">
-        <v>70135.5243</v>
+        <v>70091.1341</v>
       </c>
     </row>
     <row r="35">
@@ -11382,49 +11382,49 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>13 sep</t>
         </is>
       </c>
       <c r="AX35" t="n">
-        <v>2476.603</v>
+        <v>2525.9424</v>
       </c>
       <c r="AY35" t="n">
-        <v>2612.4033</v>
+        <v>2526.8538</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2465.4265</v>
+        <v>2462.8396</v>
       </c>
       <c r="BA35" t="n">
-        <v>2514.407</v>
+        <v>2477.0208</v>
       </c>
       <c r="BB35" t="n">
-        <v>2197.2596</v>
+        <v>2186.0397</v>
       </c>
       <c r="BC35" t="n">
-        <v>2060.2444</v>
+        <v>2057.8063</v>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>14 sep</t>
+          <t>13 sep</t>
         </is>
       </c>
       <c r="BF35" t="n">
-        <v>76830.2812</v>
+        <v>77270.17969999999</v>
       </c>
       <c r="BG35" t="n">
-        <v>79568.9531</v>
+        <v>77415.6562</v>
       </c>
       <c r="BH35" t="n">
-        <v>76367.375</v>
+        <v>76498.38280000001</v>
       </c>
       <c r="BI35" t="n">
-        <v>78163.38280000001</v>
+        <v>76838.1562</v>
       </c>
       <c r="BJ35" t="n">
-        <v>71415.9356</v>
+        <v>71159.474</v>
       </c>
       <c r="BK35" t="n">
-        <v>70189.0723</v>
+        <v>70135.5243</v>
       </c>
     </row>
     <row r="36">
@@ -11568,49 +11568,49 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="AX36" t="n">
-        <v>2514.3618</v>
+        <v>2476.603</v>
       </c>
       <c r="AY36" t="n">
-        <v>2519.3188</v>
+        <v>2612.4033</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2357.9592</v>
+        <v>2465.4265</v>
       </c>
       <c r="BA36" t="n">
-        <v>2399.0869</v>
+        <v>2514.407</v>
       </c>
       <c r="BB36" t="n">
-        <v>2207.4291</v>
+        <v>2197.2596</v>
       </c>
       <c r="BC36" t="n">
-        <v>2062.586</v>
+        <v>2060.2444</v>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>15 sep</t>
+          <t>14 sep</t>
         </is>
       </c>
       <c r="BF36" t="n">
-        <v>78162.4844</v>
+        <v>76830.2812</v>
       </c>
       <c r="BG36" t="n">
-        <v>78242.5469</v>
+        <v>79568.9531</v>
       </c>
       <c r="BH36" t="n">
-        <v>74944.5938</v>
+        <v>76367.375</v>
       </c>
       <c r="BI36" t="n">
-        <v>75612.50780000001</v>
+        <v>78163.38280000001</v>
       </c>
       <c r="BJ36" t="n">
-        <v>71653.6878</v>
+        <v>71415.9356</v>
       </c>
       <c r="BK36" t="n">
-        <v>70237.7259</v>
+        <v>70189.0723</v>
       </c>
     </row>
     <row r="37">
@@ -11754,49 +11754,49 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="AX37" t="n">
-        <v>2399.0554</v>
+        <v>2514.3618</v>
       </c>
       <c r="AY37" t="n">
-        <v>2426.9294</v>
+        <v>2519.3188</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2368.7358</v>
+        <v>2357.9592</v>
       </c>
       <c r="BA37" t="n">
-        <v>2416.1199</v>
+        <v>2399.0869</v>
       </c>
       <c r="BB37" t="n">
-        <v>2217.3525</v>
+        <v>2207.4291</v>
       </c>
       <c r="BC37" t="n">
-        <v>2064.8413</v>
+        <v>2062.586</v>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
-          <t>16 sep</t>
+          <t>15 sep</t>
         </is>
       </c>
       <c r="BF37" t="n">
-        <v>75611.7969</v>
+        <v>78162.4844</v>
       </c>
       <c r="BG37" t="n">
-        <v>76474.0781</v>
+        <v>78242.5469</v>
       </c>
       <c r="BH37" t="n">
-        <v>74995.52340000001</v>
+        <v>74944.5938</v>
       </c>
       <c r="BI37" t="n">
-        <v>76150.32030000001</v>
+        <v>75612.50780000001</v>
       </c>
       <c r="BJ37" t="n">
-        <v>71899.26700000001</v>
+        <v>71653.6878</v>
       </c>
       <c r="BK37" t="n">
-        <v>70283.4982</v>
+        <v>70237.7259</v>
       </c>
     </row>
     <row r="38">
@@ -11940,49 +11940,49 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="AX38" t="n">
-        <v>2416.1677</v>
+        <v>2399.0554</v>
       </c>
       <c r="AY38" t="n">
-        <v>2480.7371</v>
+        <v>2426.9294</v>
       </c>
       <c r="AZ38" t="n">
-        <v>2412.1877</v>
+        <v>2368.7358</v>
       </c>
       <c r="BA38" t="n">
-        <v>2447.1067</v>
+        <v>2416.1199</v>
       </c>
       <c r="BB38" t="n">
-        <v>2228.1243</v>
+        <v>2217.3525</v>
       </c>
       <c r="BC38" t="n">
-        <v>2067.3815</v>
+        <v>2064.8413</v>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>17 sep</t>
+          <t>16 sep</t>
         </is>
       </c>
       <c r="BF38" t="n">
-        <v>76152.05469999999</v>
+        <v>75611.7969</v>
       </c>
       <c r="BG38" t="n">
-        <v>77079.16409999999</v>
+        <v>76474.0781</v>
       </c>
       <c r="BH38" t="n">
-        <v>75945.55469999999</v>
+        <v>74995.52340000001</v>
       </c>
       <c r="BI38" t="n">
-        <v>76403.77340000001</v>
+        <v>76150.32030000001</v>
       </c>
       <c r="BJ38" t="n">
-        <v>72149.17909999999</v>
+        <v>71899.26700000001</v>
       </c>
       <c r="BK38" t="n">
-        <v>70336.8266</v>
+        <v>70283.4982</v>
       </c>
     </row>
     <row r="39">
@@ -12126,49 +12126,49 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="AX39" t="n">
+        <v>2416.1677</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>2480.7371</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>2412.1877</v>
+      </c>
+      <c r="BA39" t="n">
         <v>2447.1067</v>
       </c>
-      <c r="AY39" t="n">
-        <v>2643.9622</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>2435.1484</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>2611.3472</v>
-      </c>
       <c r="BB39" t="n">
-        <v>2242.0038</v>
+        <v>2228.1243</v>
       </c>
       <c r="BC39" t="n">
-        <v>2070.3019</v>
+        <v>2067.3815</v>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>18 sep</t>
+          <t>17 sep</t>
         </is>
       </c>
       <c r="BF39" t="n">
-        <v>76405.0156</v>
+        <v>76152.05469999999</v>
       </c>
       <c r="BG39" t="n">
-        <v>81331.7656</v>
+        <v>77079.16409999999</v>
       </c>
       <c r="BH39" t="n">
-        <v>76228.3281</v>
+        <v>75945.55469999999</v>
       </c>
       <c r="BI39" t="n">
-        <v>80901.46090000001</v>
+        <v>76403.77340000001</v>
       </c>
       <c r="BJ39" t="n">
-        <v>72472.70209999999</v>
+        <v>72149.17909999999</v>
       </c>
       <c r="BK39" t="n">
-        <v>70397.4546</v>
+        <v>70336.8266</v>
       </c>
     </row>
     <row r="40">
@@ -12312,49 +12312,49 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>19 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="AX40" t="n">
-        <v>2611.4563</v>
+        <v>2447.1067</v>
       </c>
       <c r="AY40" t="n">
-        <v>2659.7183</v>
+        <v>2643.9622</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2602.7368</v>
+        <v>2435.1484</v>
       </c>
       <c r="BA40" t="n">
-        <v>2631.9626</v>
+        <v>2611.3472</v>
       </c>
       <c r="BB40" t="n">
-        <v>2257.4361</v>
+        <v>2242.0038</v>
       </c>
       <c r="BC40" t="n">
-        <v>2073.5479</v>
+        <v>2070.3019</v>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
-          <t>19 sep</t>
+          <t>18 sep</t>
         </is>
       </c>
       <c r="BF40" t="n">
-        <v>80900.28909999999</v>
+        <v>76405.0156</v>
       </c>
       <c r="BG40" t="n">
-        <v>81911.1406</v>
+        <v>81331.7656</v>
       </c>
       <c r="BH40" t="n">
-        <v>80814.9375</v>
+        <v>76228.3281</v>
       </c>
       <c r="BI40" t="n">
-        <v>81233.67969999999</v>
+        <v>80901.46090000001</v>
       </c>
       <c r="BJ40" t="n">
-        <v>72841.1008</v>
+        <v>72472.70209999999</v>
       </c>
       <c r="BK40" t="n">
-        <v>70462.1548</v>
+        <v>70397.4546</v>
       </c>
     </row>
     <row r="41">
@@ -12498,49 +12498,49 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>20 sep</t>
+          <t>19 sep</t>
         </is>
       </c>
       <c r="AX41" t="n">
-        <v>2632.0146</v>
+        <v>2611.4563</v>
       </c>
       <c r="AY41" t="n">
-        <v>2647.8735</v>
+        <v>2659.7183</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2564.4326</v>
+        <v>2602.7368</v>
       </c>
       <c r="BA41" t="n">
-        <v>2642.9976</v>
+        <v>2631.9626</v>
       </c>
       <c r="BB41" t="n">
-        <v>2273.4277</v>
+        <v>2257.4361</v>
       </c>
       <c r="BC41" t="n">
-        <v>2076.1303</v>
+        <v>2073.5479</v>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
-          <t>20 sep</t>
+          <t>19 sep</t>
         </is>
       </c>
       <c r="BF41" t="n">
-        <v>81234.30469999999</v>
+        <v>80900.28909999999</v>
       </c>
       <c r="BG41" t="n">
-        <v>81455.2031</v>
+        <v>81911.1406</v>
       </c>
       <c r="BH41" t="n">
-        <v>80098.77340000001</v>
+        <v>80814.9375</v>
       </c>
       <c r="BI41" t="n">
-        <v>81142.6094</v>
+        <v>81233.67969999999</v>
       </c>
       <c r="BJ41" t="n">
-        <v>73208.6866</v>
+        <v>72841.1008</v>
       </c>
       <c r="BK41" t="n">
-        <v>70504.3149</v>
+        <v>70462.1548</v>
       </c>
     </row>
     <row r="42">
@@ -12684,49 +12684,49 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>20 sep</t>
         </is>
       </c>
       <c r="AX42" t="n">
-        <v>2642.7822</v>
+        <v>2632.0146</v>
       </c>
       <c r="AY42" t="n">
-        <v>2805.499</v>
+        <v>2647.8735</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2642.7822</v>
+        <v>2564.4326</v>
       </c>
       <c r="BA42" t="n">
-        <v>2776.4683</v>
+        <v>2642.9976</v>
       </c>
       <c r="BB42" t="n">
-        <v>2291.3066</v>
+        <v>2273.4277</v>
       </c>
       <c r="BC42" t="n">
-        <v>2079.6547</v>
+        <v>2076.1303</v>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>21 sep</t>
+          <t>20 sep</t>
         </is>
       </c>
       <c r="BF42" t="n">
-        <v>81143.625</v>
+        <v>81234.30469999999</v>
       </c>
       <c r="BG42" t="n">
-        <v>87363.75780000001</v>
+        <v>81455.2031</v>
       </c>
       <c r="BH42" t="n">
-        <v>80867.08590000001</v>
+        <v>80098.77340000001</v>
       </c>
       <c r="BI42" t="n">
-        <v>86602.91409999999</v>
+        <v>81142.6094</v>
       </c>
       <c r="BJ42" t="n">
-        <v>73671.1048</v>
+        <v>73208.6866</v>
       </c>
       <c r="BK42" t="n">
-        <v>70583.12390000001</v>
+        <v>70504.3149</v>
       </c>
     </row>
     <row r="43">
@@ -12870,49 +12870,49 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="AX43" t="n">
-        <v>2776.5803</v>
+        <v>2642.7822</v>
       </c>
       <c r="AY43" t="n">
-        <v>2776.8889</v>
+        <v>2805.499</v>
       </c>
       <c r="AZ43" t="n">
-        <v>2715.7156</v>
+        <v>2642.7822</v>
       </c>
       <c r="BA43" t="n">
-        <v>2752.6326</v>
+        <v>2776.4683</v>
       </c>
       <c r="BB43" t="n">
-        <v>2309.1941</v>
+        <v>2291.3066</v>
       </c>
       <c r="BC43" t="n">
-        <v>2083.5241</v>
+        <v>2079.6547</v>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
-          <t>22 sep</t>
+          <t>21 sep</t>
         </is>
       </c>
       <c r="BF43" t="n">
-        <v>86604.375</v>
+        <v>81143.625</v>
       </c>
       <c r="BG43" t="n">
-        <v>86700</v>
+        <v>87363.75780000001</v>
       </c>
       <c r="BH43" t="n">
-        <v>85098.00780000001</v>
+        <v>80867.08590000001</v>
       </c>
       <c r="BI43" t="n">
-        <v>86172.2812</v>
+        <v>86602.91409999999</v>
       </c>
       <c r="BJ43" t="n">
-        <v>74125.3325</v>
+        <v>73671.1048</v>
       </c>
       <c r="BK43" t="n">
-        <v>70673.3028</v>
+        <v>70583.12390000001</v>
       </c>
     </row>
     <row r="44">
@@ -13056,49 +13056,49 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="AX44" t="n">
-        <v>2752.7524</v>
+        <v>2776.5803</v>
       </c>
       <c r="AY44" t="n">
-        <v>2787.9626</v>
+        <v>2776.8889</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2636.9131</v>
+        <v>2715.7156</v>
       </c>
       <c r="BA44" t="n">
-        <v>2684.6919</v>
+        <v>2752.6326</v>
       </c>
       <c r="BB44" t="n">
-        <v>2325.5203</v>
+        <v>2309.1941</v>
       </c>
       <c r="BC44" t="n">
-        <v>2087.1002</v>
+        <v>2083.5241</v>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>23 sep</t>
+          <t>22 sep</t>
         </is>
       </c>
       <c r="BF44" t="n">
-        <v>86176.7656</v>
+        <v>86604.375</v>
       </c>
       <c r="BG44" t="n">
-        <v>87265.49219999999</v>
+        <v>86700</v>
       </c>
       <c r="BH44" t="n">
-        <v>83519.7344</v>
+        <v>85098.00780000001</v>
       </c>
       <c r="BI44" t="n">
-        <v>84383.00780000001</v>
+        <v>86172.2812</v>
       </c>
       <c r="BJ44" t="n">
-        <v>74531.87360000001</v>
+        <v>74125.3325</v>
       </c>
       <c r="BK44" t="n">
-        <v>70758.85490000001</v>
+        <v>70673.3028</v>
       </c>
     </row>
     <row r="45">
@@ -13192,7 +13192,7 @@
         <v>1502.867</v>
       </c>
       <c r="AE45" t="n">
-        <v>1301.1271</v>
+        <v>1301.1272</v>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
@@ -13242,49 +13242,49 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="AX45" t="n">
-        <v>2684.4395</v>
+        <v>2752.7524</v>
       </c>
       <c r="AY45" t="n">
-        <v>2703.6628</v>
+        <v>2787.9626</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2628.6892</v>
+        <v>2636.9131</v>
       </c>
       <c r="BA45" t="n">
-        <v>2687.3015</v>
+        <v>2684.6919</v>
       </c>
       <c r="BB45" t="n">
-        <v>2341.1358</v>
+        <v>2325.5203</v>
       </c>
       <c r="BC45" t="n">
-        <v>2090.8537</v>
+        <v>2087.1002</v>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>24 sep</t>
+          <t>23 sep</t>
         </is>
       </c>
       <c r="BF45" t="n">
-        <v>84381.5938</v>
+        <v>86176.7656</v>
       </c>
       <c r="BG45" t="n">
-        <v>84876.22659999999</v>
+        <v>87265.49219999999</v>
       </c>
       <c r="BH45" t="n">
-        <v>82906.61719999999</v>
+        <v>83519.7344</v>
       </c>
       <c r="BI45" t="n">
-        <v>84379.0625</v>
+        <v>84383.00780000001</v>
       </c>
       <c r="BJ45" t="n">
-        <v>74927.5048</v>
+        <v>74531.87360000001</v>
       </c>
       <c r="BK45" t="n">
-        <v>70850.9013</v>
+        <v>70758.85490000001</v>
       </c>
     </row>
     <row r="46">
@@ -13428,49 +13428,49 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="AX46" t="n">
-        <v>2687.3225</v>
+        <v>2684.4395</v>
       </c>
       <c r="AY46" t="n">
-        <v>2741.2969</v>
+        <v>2703.6628</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2667.0452</v>
+        <v>2628.6892</v>
       </c>
       <c r="BA46" t="n">
-        <v>2690.4756</v>
+        <v>2687.3015</v>
       </c>
       <c r="BB46" t="n">
-        <v>2356.9041</v>
+        <v>2341.1358</v>
       </c>
       <c r="BC46" t="n">
-        <v>2094.3414</v>
+        <v>2090.8537</v>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>25 sep</t>
+          <t>24 sep</t>
         </is>
       </c>
       <c r="BF46" t="n">
-        <v>84379.5156</v>
+        <v>84381.5938</v>
       </c>
       <c r="BG46" t="n">
-        <v>85230.05469999999</v>
+        <v>84876.22659999999</v>
       </c>
       <c r="BH46" t="n">
-        <v>83165.5312</v>
+        <v>82906.61719999999</v>
       </c>
       <c r="BI46" t="n">
-        <v>84034.9219</v>
+        <v>84379.0625</v>
       </c>
       <c r="BJ46" t="n">
-        <v>75322.961</v>
+        <v>74927.5048</v>
       </c>
       <c r="BK46" t="n">
-        <v>70929.064</v>
+        <v>70850.9013</v>
       </c>
     </row>
     <row r="47">
@@ -13614,49 +13614,49 @@
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>26 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="AX47" t="n">
-        <v>2690.4817</v>
+        <v>2687.3225</v>
       </c>
       <c r="AY47" t="n">
-        <v>2696.9961</v>
+        <v>2741.2969</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2665.8625</v>
+        <v>2667.0452</v>
       </c>
       <c r="BA47" t="n">
-        <v>2695.2131</v>
+        <v>2690.4756</v>
       </c>
       <c r="BB47" t="n">
-        <v>2372.5428</v>
+        <v>2356.9041</v>
       </c>
       <c r="BC47" t="n">
-        <v>2097.6319</v>
+        <v>2094.3414</v>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>26 sep</t>
+          <t>25 sep</t>
         </is>
       </c>
       <c r="BF47" t="n">
-        <v>84035.82030000001</v>
+        <v>84379.5156</v>
       </c>
       <c r="BG47" t="n">
-        <v>84423.17969999999</v>
+        <v>85230.05469999999</v>
       </c>
       <c r="BH47" t="n">
-        <v>83781.1094</v>
+        <v>83165.5312</v>
       </c>
       <c r="BI47" t="n">
-        <v>84406.4531</v>
+        <v>84034.9219</v>
       </c>
       <c r="BJ47" t="n">
-        <v>75713.4863</v>
+        <v>75322.961</v>
       </c>
       <c r="BK47" t="n">
-        <v>71001.4616</v>
+        <v>70929.064</v>
       </c>
     </row>
     <row r="48">
@@ -13800,49 +13800,49 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>27 sep</t>
+          <t>26 sep</t>
         </is>
       </c>
       <c r="AX48" t="n">
-        <v>2695.3489</v>
+        <v>2690.4817</v>
       </c>
       <c r="AY48" t="n">
-        <v>2722.0393</v>
+        <v>2696.9961</v>
       </c>
       <c r="AZ48" t="n">
-        <v>2669.4727</v>
+        <v>2665.8625</v>
       </c>
       <c r="BA48" t="n">
-        <v>2686.9268</v>
+        <v>2695.2131</v>
       </c>
       <c r="BB48" t="n">
-        <v>2387.9707</v>
+        <v>2372.5428</v>
       </c>
       <c r="BC48" t="n">
-        <v>2100.8087</v>
+        <v>2097.6319</v>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>27 sep</t>
+          <t>26 sep</t>
         </is>
       </c>
       <c r="BF48" t="n">
-        <v>84412.7188</v>
+        <v>84035.82030000001</v>
       </c>
       <c r="BG48" t="n">
-        <v>85126.1094</v>
+        <v>84423.17969999999</v>
       </c>
       <c r="BH48" t="n">
-        <v>84121.3281</v>
+        <v>83781.1094</v>
       </c>
       <c r="BI48" t="n">
-        <v>84458.08590000001</v>
+        <v>84406.4531</v>
       </c>
       <c r="BJ48" t="n">
-        <v>76104.5542</v>
+        <v>75713.4863</v>
       </c>
       <c r="BK48" t="n">
-        <v>71072.7277</v>
+        <v>71001.4616</v>
       </c>
     </row>
     <row r="49">
@@ -13986,49 +13986,49 @@
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>27 sep</t>
         </is>
       </c>
       <c r="AX49" t="n">
-        <v>2687.0007</v>
+        <v>2695.3489</v>
       </c>
       <c r="AY49" t="n">
-        <v>2718.8086</v>
+        <v>2722.0393</v>
       </c>
       <c r="AZ49" t="n">
-        <v>2635.4846</v>
+        <v>2669.4727</v>
       </c>
       <c r="BA49" t="n">
-        <v>2688.6687</v>
+        <v>2686.9268</v>
       </c>
       <c r="BB49" t="n">
-        <v>2403.5704</v>
+        <v>2387.9707</v>
       </c>
       <c r="BC49" t="n">
-        <v>2103.8863</v>
+        <v>2100.8087</v>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>28 sep</t>
+          <t>27 sep</t>
         </is>
       </c>
       <c r="BF49" t="n">
-        <v>84454.11719999999</v>
+        <v>84412.7188</v>
       </c>
       <c r="BG49" t="n">
-        <v>84972.66409999999</v>
+        <v>85126.1094</v>
       </c>
       <c r="BH49" t="n">
-        <v>82570.7188</v>
+        <v>84121.3281</v>
       </c>
       <c r="BI49" t="n">
-        <v>83502.6094</v>
+        <v>84458.08590000001</v>
       </c>
       <c r="BJ49" t="n">
-        <v>76477.7087</v>
+        <v>76104.5542</v>
       </c>
       <c r="BK49" t="n">
-        <v>71137.77340000001</v>
+        <v>71072.7277</v>
       </c>
     </row>
     <row r="50">
@@ -14172,49 +14172,49 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="AX50" t="n">
-        <v>2688.634</v>
+        <v>2687.0007</v>
       </c>
       <c r="AY50" t="n">
-        <v>2746.0107</v>
+        <v>2718.8086</v>
       </c>
       <c r="AZ50" t="n">
-        <v>2651.4714</v>
+        <v>2635.4846</v>
       </c>
       <c r="BA50" t="n">
-        <v>2676.7222</v>
+        <v>2688.6687</v>
       </c>
       <c r="BB50" t="n">
-        <v>2419.6793</v>
+        <v>2403.5704</v>
       </c>
       <c r="BC50" t="n">
-        <v>2106.8071</v>
+        <v>2103.8863</v>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>29 sep</t>
+          <t>28 sep</t>
         </is>
       </c>
       <c r="BF50" t="n">
-        <v>83500.32030000001</v>
+        <v>84454.11719999999</v>
       </c>
       <c r="BG50" t="n">
-        <v>84511.2812</v>
+        <v>84972.66409999999</v>
       </c>
       <c r="BH50" t="n">
-        <v>82739.0938</v>
+        <v>82570.7188</v>
       </c>
       <c r="BI50" t="n">
-        <v>83622.42969999999</v>
+        <v>83502.6094</v>
       </c>
       <c r="BJ50" t="n">
-        <v>76871.9455</v>
+        <v>76477.7087</v>
       </c>
       <c r="BK50" t="n">
-        <v>71201.0442</v>
+        <v>71137.77340000001</v>
       </c>
     </row>
     <row r="51">
@@ -14358,49 +14358,49 @@
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="AX51" t="n">
-        <v>2676.6921</v>
+        <v>2688.634</v>
       </c>
       <c r="AY51" t="n">
-        <v>2737.2649</v>
+        <v>2746.0107</v>
       </c>
       <c r="AZ51" t="n">
-        <v>2657.0854</v>
+        <v>2651.4714</v>
       </c>
       <c r="BA51" t="n">
-        <v>2683.6794</v>
+        <v>2676.7222</v>
       </c>
       <c r="BB51" t="n">
-        <v>2435.7254</v>
+        <v>2419.6793</v>
       </c>
       <c r="BC51" t="n">
-        <v>2109.7401</v>
+        <v>2106.8071</v>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>30 sep</t>
+          <t>29 sep</t>
         </is>
       </c>
       <c r="BF51" t="n">
-        <v>83621.39840000001</v>
+        <v>83500.32030000001</v>
       </c>
       <c r="BG51" t="n">
-        <v>85599.80469999999</v>
+        <v>84511.2812</v>
       </c>
       <c r="BH51" t="n">
-        <v>82927.875</v>
+        <v>82739.0938</v>
       </c>
       <c r="BI51" t="n">
-        <v>83553.85159999999</v>
+        <v>83622.42969999999</v>
       </c>
       <c r="BJ51" t="n">
-        <v>77271.98510000001</v>
+        <v>76871.9455</v>
       </c>
       <c r="BK51" t="n">
-        <v>71262.7404</v>
+        <v>71201.0442</v>
       </c>
     </row>
     <row r="52">
@@ -14544,49 +14544,49 @@
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="AX52" t="n">
-        <v>2683.8191</v>
+        <v>2676.6921</v>
       </c>
       <c r="AY52" t="n">
-        <v>2720.188</v>
+        <v>2737.2649</v>
       </c>
       <c r="AZ52" t="n">
-        <v>2672.7065</v>
+        <v>2657.0854</v>
       </c>
       <c r="BA52" t="n">
-        <v>2705.5371</v>
+        <v>2683.6794</v>
       </c>
       <c r="BB52" t="n">
-        <v>2452.2734</v>
+        <v>2435.7254</v>
       </c>
       <c r="BC52" t="n">
-        <v>2112.3804</v>
+        <v>2109.7401</v>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>1 okt</t>
+          <t>30 sep</t>
         </is>
       </c>
       <c r="BF52" t="n">
-        <v>83554.25</v>
+        <v>83621.39840000001</v>
       </c>
       <c r="BG52" t="n">
-        <v>85224.27340000001</v>
+        <v>85599.80469999999</v>
       </c>
       <c r="BH52" t="n">
-        <v>83132.75780000001</v>
+        <v>82927.875</v>
       </c>
       <c r="BI52" t="n">
-        <v>84853.10159999999</v>
+        <v>83553.85159999999</v>
       </c>
       <c r="BJ52" t="n">
-        <v>77700.9984</v>
+        <v>77271.98510000001</v>
       </c>
       <c r="BK52" t="n">
-        <v>71323.0563</v>
+        <v>71262.7404</v>
       </c>
     </row>
     <row r="53">
@@ -14730,49 +14730,49 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="AX53" t="n">
-        <v>2705.7256</v>
+        <v>2683.8191</v>
       </c>
       <c r="AY53" t="n">
-        <v>2773.5249</v>
+        <v>2720.188</v>
       </c>
       <c r="AZ53" t="n">
-        <v>2651.0835</v>
+        <v>2672.7065</v>
       </c>
       <c r="BA53" t="n">
-        <v>2668.1511</v>
+        <v>2705.5371</v>
       </c>
       <c r="BB53" t="n">
-        <v>2467.9566</v>
+        <v>2452.2734</v>
       </c>
       <c r="BC53" t="n">
-        <v>2113.9653</v>
+        <v>2112.3804</v>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>2 okt</t>
+          <t>1 okt</t>
         </is>
       </c>
       <c r="BF53" t="n">
-        <v>84855.64840000001</v>
+        <v>83554.25</v>
       </c>
       <c r="BG53" t="n">
-        <v>87146.35159999999</v>
+        <v>85224.27340000001</v>
       </c>
       <c r="BH53" t="n">
-        <v>83852.69530000001</v>
+        <v>83132.75780000001</v>
       </c>
       <c r="BI53" t="n">
-        <v>84497.21090000001</v>
+        <v>84853.10159999999</v>
       </c>
       <c r="BJ53" t="n">
-        <v>78122.8992</v>
+        <v>77700.9984</v>
       </c>
       <c r="BK53" t="n">
-        <v>71371.2369</v>
+        <v>71323.0563</v>
       </c>
     </row>
     <row r="54">
@@ -14916,49 +14916,49 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>3 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="AX54" t="n">
-        <v>2668.4485</v>
+        <v>2705.7256</v>
       </c>
       <c r="AY54" t="n">
-        <v>2689.594</v>
+        <v>2773.5249</v>
       </c>
       <c r="AZ54" t="n">
-        <v>2665.4348</v>
+        <v>2651.0835</v>
       </c>
       <c r="BA54" t="n">
-        <v>2687.2554</v>
+        <v>2668.1511</v>
       </c>
       <c r="BB54" t="n">
-        <v>2484.0887</v>
+        <v>2467.9566</v>
       </c>
       <c r="BC54" t="n">
-        <v>2115.8113</v>
+        <v>2113.9653</v>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>3 okt</t>
+          <t>2 okt</t>
         </is>
       </c>
       <c r="BF54" t="n">
-        <v>84503.1875</v>
+        <v>84855.64840000001</v>
       </c>
       <c r="BG54" t="n">
-        <v>85019.3281</v>
+        <v>87146.35159999999</v>
       </c>
       <c r="BH54" t="n">
-        <v>84429.64840000001</v>
+        <v>83852.69530000001</v>
       </c>
       <c r="BI54" t="n">
-        <v>84763.5781</v>
+        <v>84497.21090000001</v>
       </c>
       <c r="BJ54" t="n">
-        <v>78558.65889999999</v>
+        <v>78122.8992</v>
       </c>
       <c r="BK54" t="n">
-        <v>71425.4424</v>
+        <v>71371.2369</v>
       </c>
     </row>
     <row r="55">
@@ -15102,49 +15102,49 @@
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>4 okt</t>
+          <t>3 okt</t>
         </is>
       </c>
       <c r="AX55" t="n">
-        <v>2687.3511</v>
+        <v>2668.4485</v>
       </c>
       <c r="AY55" t="n">
-        <v>2738.2566</v>
+        <v>2689.594</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2686.1321</v>
+        <v>2665.4348</v>
       </c>
       <c r="BA55" t="n">
-        <v>2726.509</v>
+        <v>2687.2554</v>
       </c>
       <c r="BB55" t="n">
-        <v>2501.0007</v>
+        <v>2484.0887</v>
       </c>
       <c r="BC55" t="n">
-        <v>2118.4254</v>
+        <v>2115.8113</v>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>4 okt</t>
+          <t>3 okt</t>
         </is>
       </c>
       <c r="BF55" t="n">
-        <v>84765.5156</v>
+        <v>84503.1875</v>
       </c>
       <c r="BG55" t="n">
-        <v>86766.14840000001</v>
+        <v>85019.3281</v>
       </c>
       <c r="BH55" t="n">
-        <v>84707.32030000001</v>
+        <v>84429.64840000001</v>
       </c>
       <c r="BI55" t="n">
-        <v>86480.30469999999</v>
+        <v>84763.5781</v>
       </c>
       <c r="BJ55" t="n">
-        <v>79027.77860000001</v>
+        <v>78558.65889999999</v>
       </c>
       <c r="BK55" t="n">
-        <v>71501.6161</v>
+        <v>71425.4424</v>
       </c>
     </row>
     <row r="56">
@@ -15238,7 +15238,7 @@
         <v>1490.0724</v>
       </c>
       <c r="AE56" t="n">
-        <v>1332.1047</v>
+        <v>1332.1048</v>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
@@ -15288,49 +15288,49 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>4 okt</t>
         </is>
       </c>
       <c r="AX56" t="n">
-        <v>2726.6538</v>
+        <v>2687.3511</v>
       </c>
       <c r="AY56" t="n">
-        <v>2736.7852</v>
+        <v>2738.2566</v>
       </c>
       <c r="AZ56" t="n">
-        <v>2679.355</v>
+        <v>2686.1321</v>
       </c>
       <c r="BA56" t="n">
-        <v>2711.0315</v>
+        <v>2726.509</v>
       </c>
       <c r="BB56" t="n">
-        <v>2517.7425</v>
+        <v>2501.0007</v>
       </c>
       <c r="BC56" t="n">
-        <v>2121.2935</v>
+        <v>2118.4254</v>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>5 okt</t>
+          <t>4 okt</t>
         </is>
       </c>
       <c r="BF56" t="n">
-        <v>86480.00780000001</v>
+        <v>84765.5156</v>
       </c>
       <c r="BG56" t="n">
-        <v>86971.7812</v>
+        <v>86766.14840000001</v>
       </c>
       <c r="BH56" t="n">
-        <v>84971.86719999999</v>
+        <v>84707.32030000001</v>
       </c>
       <c r="BI56" t="n">
-        <v>85786.5938</v>
+        <v>86480.30469999999</v>
       </c>
       <c r="BJ56" t="n">
-        <v>79487.13740000001</v>
+        <v>79027.77860000001</v>
       </c>
       <c r="BK56" t="n">
-        <v>71580.98510000001</v>
+        <v>71501.6161</v>
       </c>
     </row>
     <row r="57">
@@ -15474,49 +15474,49 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="AX57" t="n">
-        <v>2711.0271</v>
+        <v>2726.6538</v>
       </c>
       <c r="AY57" t="n">
-        <v>2723.7361</v>
+        <v>2736.7852</v>
       </c>
       <c r="AZ57" t="n">
-        <v>2683.8933</v>
+        <v>2679.355</v>
       </c>
       <c r="BA57" t="n">
-        <v>2697.5164</v>
+        <v>2711.0315</v>
       </c>
       <c r="BB57" t="n">
-        <v>2533.4488</v>
+        <v>2517.7425</v>
       </c>
       <c r="BC57" t="n">
-        <v>2124.0486</v>
+        <v>2121.2935</v>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>6 okt</t>
+          <t>5 okt</t>
         </is>
       </c>
       <c r="BF57" t="n">
-        <v>85785.66409999999</v>
+        <v>86480.00780000001</v>
       </c>
       <c r="BG57" t="n">
-        <v>86664.53909999999</v>
+        <v>86971.7812</v>
       </c>
       <c r="BH57" t="n">
-        <v>85119.55469999999</v>
+        <v>84971.86719999999</v>
       </c>
       <c r="BI57" t="n">
-        <v>85557.5625</v>
+        <v>85786.5938</v>
       </c>
       <c r="BJ57" t="n">
-        <v>79908.1636</v>
+        <v>79487.13740000001</v>
       </c>
       <c r="BK57" t="n">
-        <v>71656.16</v>
+        <v>71580.98510000001</v>
       </c>
     </row>
     <row r="58">
@@ -15660,49 +15660,49 @@
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="AX58" t="n">
-        <v>2697.3748</v>
+        <v>2711.0271</v>
       </c>
       <c r="AY58" t="n">
-        <v>2699.259</v>
+        <v>2723.7361</v>
       </c>
       <c r="AZ58" t="n">
-        <v>2540.5916</v>
+        <v>2683.8933</v>
       </c>
       <c r="BA58" t="n">
-        <v>2573.5273</v>
+        <v>2697.5164</v>
       </c>
       <c r="BB58" t="n">
-        <v>2546.5902</v>
+        <v>2533.4488</v>
       </c>
       <c r="BC58" t="n">
-        <v>2126.5328</v>
+        <v>2124.0486</v>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>7 okt</t>
+          <t>6 okt</t>
         </is>
       </c>
       <c r="BF58" t="n">
-        <v>85554.7969</v>
+        <v>85785.66409999999</v>
       </c>
       <c r="BG58" t="n">
-        <v>85594.5469</v>
+        <v>86664.53909999999</v>
       </c>
       <c r="BH58" t="n">
-        <v>82771.78909999999</v>
+        <v>85119.55469999999</v>
       </c>
       <c r="BI58" t="n">
-        <v>83275.92969999999</v>
+        <v>85557.5625</v>
       </c>
       <c r="BJ58" t="n">
-        <v>80280.068</v>
+        <v>79908.1636</v>
       </c>
       <c r="BK58" t="n">
-        <v>71728.982</v>
+        <v>71656.16</v>
       </c>
     </row>
     <row r="59">
@@ -15846,49 +15846,49 @@
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="AX59" t="n">
-        <v>2573.5547</v>
+        <v>2697.3748</v>
       </c>
       <c r="AY59" t="n">
-        <v>2585.303</v>
+        <v>2699.259</v>
       </c>
       <c r="AZ59" t="n">
-        <v>2406.1519</v>
+        <v>2540.5916</v>
       </c>
       <c r="BA59" t="n">
-        <v>2471.9126</v>
+        <v>2573.5273</v>
       </c>
       <c r="BB59" t="n">
-        <v>2550.9992</v>
+        <v>2546.5902</v>
       </c>
       <c r="BC59" t="n">
-        <v>2128.6271</v>
+        <v>2126.5328</v>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>8 okt</t>
+          <t>7 okt</t>
         </is>
       </c>
       <c r="BF59" t="n">
-        <v>83281.4688</v>
+        <v>85554.7969</v>
       </c>
       <c r="BG59" t="n">
-        <v>83474.96090000001</v>
+        <v>85594.5469</v>
       </c>
       <c r="BH59" t="n">
-        <v>80336.9062</v>
+        <v>82771.78909999999</v>
       </c>
       <c r="BI59" t="n">
-        <v>81676.33590000001</v>
+        <v>83275.92969999999</v>
       </c>
       <c r="BJ59" t="n">
-        <v>80528.2709</v>
+        <v>80280.068</v>
       </c>
       <c r="BK59" t="n">
-        <v>71798.1376</v>
+        <v>71728.982</v>
       </c>
     </row>
     <row r="60">
@@ -16032,49 +16032,49 @@
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="AX60" t="n">
+        <v>2573.5547</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>2585.303</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>2406.1519</v>
+      </c>
+      <c r="BA60" t="n">
         <v>2471.9126</v>
       </c>
-      <c r="AY60" t="n">
-        <v>2514.897</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>2469.229</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>2485.5386</v>
-      </c>
       <c r="BB60" t="n">
-        <v>2554.1823</v>
+        <v>2550.9992</v>
       </c>
       <c r="BC60" t="n">
-        <v>2130.2941</v>
+        <v>2128.6271</v>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
-          <t>9 okt</t>
+          <t>8 okt</t>
         </is>
       </c>
       <c r="BF60" t="n">
+        <v>83281.4688</v>
+      </c>
+      <c r="BG60" t="n">
+        <v>83474.96090000001</v>
+      </c>
+      <c r="BH60" t="n">
+        <v>80336.9062</v>
+      </c>
+      <c r="BI60" t="n">
         <v>81676.33590000001</v>
       </c>
-      <c r="BG60" t="n">
-        <v>83418.2969</v>
-      </c>
-      <c r="BH60" t="n">
-        <v>81557.7031</v>
-      </c>
-      <c r="BI60" t="n">
-        <v>82546.32030000001</v>
-      </c>
       <c r="BJ60" t="n">
-        <v>80718.5422</v>
+        <v>80528.2709</v>
       </c>
       <c r="BK60" t="n">
-        <v>71856.29489999999</v>
+        <v>71798.1376</v>
       </c>
     </row>
     <row r="61">
@@ -16218,49 +16218,49 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>10 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="AX61" t="n">
+        <v>2471.9126</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>2514.897</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>2469.229</v>
+      </c>
+      <c r="BA61" t="n">
         <v>2485.5386</v>
       </c>
-      <c r="AY61" t="n">
-        <v>2516.6155</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>2483.7974</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>2504.0278</v>
-      </c>
       <c r="BB61" t="n">
-        <v>2553.9572</v>
+        <v>2554.1823</v>
       </c>
       <c r="BC61" t="n">
-        <v>2132.0357</v>
+        <v>2130.2941</v>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
-          <t>10 okt</t>
+          <t>9 okt</t>
         </is>
       </c>
       <c r="BF61" t="n">
+        <v>81676.33590000001</v>
+      </c>
+      <c r="BG61" t="n">
+        <v>83418.2969</v>
+      </c>
+      <c r="BH61" t="n">
+        <v>81557.7031</v>
+      </c>
+      <c r="BI61" t="n">
         <v>82546.32030000001</v>
       </c>
-      <c r="BG61" t="n">
-        <v>83092.0312</v>
-      </c>
-      <c r="BH61" t="n">
-        <v>82473.03909999999</v>
-      </c>
-      <c r="BI61" t="n">
-        <v>82912.22659999999</v>
-      </c>
       <c r="BJ61" t="n">
-        <v>80810.083</v>
+        <v>80718.5422</v>
       </c>
       <c r="BK61" t="n">
-        <v>71918.2668</v>
+        <v>71856.29489999999</v>
       </c>
     </row>
     <row r="62">
@@ -16404,49 +16404,49 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>11 okt</t>
+          <t>10 okt</t>
         </is>
       </c>
       <c r="AX62" t="n">
+        <v>2485.5386</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>2516.6155</v>
+      </c>
+      <c r="AZ62" t="n">
+        <v>2483.7974</v>
+      </c>
+      <c r="BA62" t="n">
         <v>2504.0278</v>
       </c>
-      <c r="AY62" t="n">
-        <v>2551.5315</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>2495.7202</v>
-      </c>
-      <c r="BA62" t="n">
-        <v>2534.6992</v>
-      </c>
       <c r="BB62" t="n">
-        <v>2556.1662</v>
+        <v>2553.9572</v>
       </c>
       <c r="BC62" t="n">
-        <v>2133.8691</v>
+        <v>2132.0357</v>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>11 okt</t>
+          <t>10 okt</t>
         </is>
       </c>
       <c r="BF62" t="n">
+        <v>82546.32030000001</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>83092.0312</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>82473.03909999999</v>
+      </c>
+      <c r="BI62" t="n">
         <v>82912.22659999999</v>
       </c>
-      <c r="BG62" t="n">
-        <v>84103.625</v>
-      </c>
-      <c r="BH62" t="n">
-        <v>82722.1094</v>
-      </c>
-      <c r="BI62" t="n">
-        <v>83679.4688</v>
-      </c>
       <c r="BJ62" t="n">
-        <v>80942.00410000001</v>
+        <v>80810.083</v>
       </c>
       <c r="BK62" t="n">
-        <v>71980.11470000001</v>
+        <v>71918.2668</v>
       </c>
     </row>
     <row r="63">
@@ -16590,49 +16590,49 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>11 okt</t>
         </is>
       </c>
       <c r="AX63" t="n">
+        <v>2504.0278</v>
+      </c>
+      <c r="AY63" t="n">
+        <v>2551.5315</v>
+      </c>
+      <c r="AZ63" t="n">
+        <v>2495.7202</v>
+      </c>
+      <c r="BA63" t="n">
         <v>2534.6992</v>
       </c>
-      <c r="AY63" t="n">
-        <v>2576.5774</v>
-      </c>
-      <c r="AZ63" t="n">
-        <v>2441.6763</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>2444.3574</v>
-      </c>
       <c r="BB63" t="n">
-        <v>2555.777</v>
+        <v>2556.1662</v>
       </c>
       <c r="BC63" t="n">
-        <v>2135.793</v>
+        <v>2133.8691</v>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>12 okt</t>
+          <t>11 okt</t>
         </is>
       </c>
       <c r="BF63" t="n">
+        <v>82912.22659999999</v>
+      </c>
+      <c r="BG63" t="n">
+        <v>84103.625</v>
+      </c>
+      <c r="BH63" t="n">
+        <v>82722.1094</v>
+      </c>
+      <c r="BI63" t="n">
         <v>83679.4688</v>
       </c>
-      <c r="BG63" t="n">
-        <v>84249.2188</v>
-      </c>
-      <c r="BH63" t="n">
-        <v>81681.63280000001</v>
-      </c>
-      <c r="BI63" t="n">
-        <v>81762.5625</v>
-      </c>
       <c r="BJ63" t="n">
-        <v>81022.14999999999</v>
+        <v>80942.00410000001</v>
       </c>
       <c r="BK63" t="n">
-        <v>72044.9694</v>
+        <v>71980.11470000001</v>
       </c>
     </row>
     <row r="64">
@@ -16776,49 +16776,49 @@
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="AX64" t="n">
+        <v>2534.6992</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>2576.5774</v>
+      </c>
+      <c r="AZ64" t="n">
+        <v>2441.6763</v>
+      </c>
+      <c r="BA64" t="n">
         <v>2444.3574</v>
       </c>
-      <c r="AY64" t="n">
-        <v>2534.77</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>2407.6274</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>2496.6255</v>
-      </c>
       <c r="BB64" t="n">
-        <v>2556.0729</v>
+        <v>2555.777</v>
       </c>
       <c r="BC64" t="n">
-        <v>2138.3197</v>
+        <v>2135.793</v>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>13 okt</t>
+          <t>12 okt</t>
         </is>
       </c>
       <c r="BF64" t="n">
+        <v>83679.4688</v>
+      </c>
+      <c r="BG64" t="n">
+        <v>84249.2188</v>
+      </c>
+      <c r="BH64" t="n">
+        <v>81681.63280000001</v>
+      </c>
+      <c r="BI64" t="n">
         <v>81762.5625</v>
       </c>
-      <c r="BG64" t="n">
-        <v>84061.0938</v>
-      </c>
-      <c r="BH64" t="n">
-        <v>80962.5156</v>
-      </c>
-      <c r="BI64" t="n">
-        <v>83095.125</v>
-      </c>
       <c r="BJ64" t="n">
-        <v>81104.7628</v>
+        <v>81022.14999999999</v>
       </c>
       <c r="BK64" t="n">
-        <v>72128.7531</v>
+        <v>72044.9694</v>
       </c>
     </row>
     <row r="65">
@@ -16962,74 +16962,74 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="AX65" t="n">
+        <v>2444.3574</v>
+      </c>
+      <c r="AY65" t="n">
+        <v>2534.77</v>
+      </c>
+      <c r="AZ65" t="n">
+        <v>2407.6274</v>
+      </c>
+      <c r="BA65" t="n">
         <v>2496.6255</v>
       </c>
-      <c r="AY65" t="n">
-        <v>2526.0706</v>
-      </c>
-      <c r="AZ65" t="n">
-        <v>2403.2107</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>2418.207</v>
-      </c>
       <c r="BB65" t="n">
-        <v>2555.5739</v>
+        <v>2556.0729</v>
       </c>
       <c r="BC65" t="n">
-        <v>2140.4473</v>
+        <v>2138.3197</v>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
-          <t>14 okt</t>
+          <t>13 okt</t>
         </is>
       </c>
       <c r="BF65" t="n">
+        <v>81762.5625</v>
+      </c>
+      <c r="BG65" t="n">
+        <v>84061.0938</v>
+      </c>
+      <c r="BH65" t="n">
+        <v>80962.5156</v>
+      </c>
+      <c r="BI65" t="n">
         <v>83095.125</v>
       </c>
-      <c r="BG65" t="n">
-        <v>84049.0625</v>
-      </c>
-      <c r="BH65" t="n">
-        <v>81345.88280000001</v>
-      </c>
-      <c r="BI65" t="n">
-        <v>81562.49219999999</v>
-      </c>
       <c r="BJ65" t="n">
-        <v>81164.71309999999</v>
+        <v>81104.7628</v>
       </c>
       <c r="BK65" t="n">
-        <v>72204.96709999999</v>
+        <v>72128.7531</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>129.97</v>
+        <v>132.08</v>
       </c>
       <c r="C66" t="n">
-        <v>130.18</v>
+        <v>132.42</v>
       </c>
       <c r="D66" t="n">
-        <v>129.94</v>
+        <v>131.75</v>
       </c>
       <c r="E66" t="n">
-        <v>130.18</v>
+        <v>131.78</v>
       </c>
       <c r="F66" t="n">
-        <v>128.2818</v>
+        <v>128.3138</v>
       </c>
       <c r="G66" t="n">
-        <v>120.3785</v>
+        <v>120.3865</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>982.2577</v>
       </c>
       <c r="O66" t="n">
-        <v>711.5055</v>
+        <v>711.5056</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -17079,49 +17079,49 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>1451.8</v>
+        <v>1510</v>
       </c>
       <c r="AA66" t="n">
-        <v>1455</v>
+        <v>1564</v>
       </c>
       <c r="AB66" t="n">
-        <v>1422.6</v>
+        <v>1494</v>
       </c>
       <c r="AC66" t="n">
-        <v>1441</v>
+        <v>1534.8</v>
       </c>
       <c r="AD66" t="n">
-        <v>1517.28</v>
+        <v>1519.156</v>
       </c>
       <c r="AE66" t="n">
-        <v>1366.3805</v>
+        <v>1366.8495</v>
       </c>
       <c r="AG66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>50.7</v>
+        <v>56.64</v>
       </c>
       <c r="AI66" t="n">
-        <v>51.4</v>
+        <v>58.01</v>
       </c>
       <c r="AJ66" t="n">
-        <v>49.9</v>
+        <v>54.65</v>
       </c>
       <c r="AK66" t="n">
-        <v>50.53</v>
+        <v>55.05</v>
       </c>
       <c r="AL66" t="n">
-        <v>58.0658</v>
+        <v>58.1562</v>
       </c>
       <c r="AM66" t="n">
-        <v>56.4442</v>
+        <v>56.4668</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -17148,49 +17148,49 @@
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="AX66" t="n">
-        <v>2418.4326</v>
+        <v>2496.6255</v>
       </c>
       <c r="AY66" t="n">
-        <v>2424.9353</v>
+        <v>2526.0706</v>
       </c>
       <c r="AZ66" t="n">
-        <v>2342.5146</v>
+        <v>2403.2107</v>
       </c>
       <c r="BA66" t="n">
-        <v>2376.51</v>
+        <v>2418.207</v>
       </c>
       <c r="BB66" t="n">
-        <v>2552.9789</v>
+        <v>2555.5739</v>
       </c>
       <c r="BC66" t="n">
-        <v>2142.417</v>
+        <v>2140.4473</v>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
-          <t>15 okt</t>
+          <t>14 okt</t>
         </is>
       </c>
       <c r="BF66" t="n">
-        <v>81573.10159999999</v>
+        <v>83095.125</v>
       </c>
       <c r="BG66" t="n">
-        <v>81773.7656</v>
+        <v>84049.0625</v>
       </c>
       <c r="BH66" t="n">
-        <v>80474.07030000001</v>
+        <v>81345.88280000001</v>
       </c>
       <c r="BI66" t="n">
-        <v>81413.99219999999</v>
+        <v>81562.49219999999</v>
       </c>
       <c r="BJ66" t="n">
-        <v>81212.4445</v>
+        <v>81164.71309999999</v>
       </c>
       <c r="BK66" t="n">
-        <v>72282.2625</v>
+        <v>72204.96709999999</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/investeerder.xlsx
+++ b/rapporten/investeerder.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9803.040000000001</v>
+        <v>9799.15</v>
       </c>
       <c r="C4" s="2">
         <f>B4-B3</f>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.612</v>
+        <v>0.6122</v>
       </c>
     </row>
     <row r="3">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.0585</v>
+        <v>0.0584</v>
       </c>
     </row>
     <row r="5">
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.0582</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="6">
@@ -4300,7 +4300,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.0563</v>
+        <v>0.0562</v>
       </c>
     </row>
     <row r="8">
@@ -5703,7 +5703,7 @@
         <v>865.3239</v>
       </c>
       <c r="N5" t="n">
-        <v>937.4059999999999</v>
+        <v>937.4059</v>
       </c>
       <c r="O5" t="n">
         <v>486.3243</v>
@@ -6075,7 +6075,7 @@
         <v>959.329</v>
       </c>
       <c r="N7" t="n">
-        <v>948.1458</v>
+        <v>948.1457</v>
       </c>
       <c r="O7" t="n">
         <v>494.148</v>
@@ -6447,7 +6447,7 @@
         <v>920.8051</v>
       </c>
       <c r="N9" t="n">
-        <v>955.1345</v>
+        <v>955.1344</v>
       </c>
       <c r="O9" t="n">
         <v>501.8105</v>
@@ -7005,7 +7005,7 @@
         <v>738.8837</v>
       </c>
       <c r="N12" t="n">
-        <v>958.2497</v>
+        <v>958.2496</v>
       </c>
       <c r="O12" t="n">
         <v>511.2377</v>
@@ -7240,7 +7240,7 @@
         <v>1535.6006</v>
       </c>
       <c r="AE13" t="n">
-        <v>1204.2381</v>
+        <v>1204.238</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>1541.0191</v>
       </c>
       <c r="AE17" t="n">
-        <v>1215.9399</v>
+        <v>1215.9398</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>877.4319</v>
       </c>
       <c r="N19" t="n">
-        <v>970.7131000000001</v>
+        <v>970.713</v>
       </c>
       <c r="O19" t="n">
         <v>534.7758</v>
@@ -9795,7 +9795,7 @@
         <v>936.9625</v>
       </c>
       <c r="N27" t="n">
-        <v>962.1174999999999</v>
+        <v>962.1174</v>
       </c>
       <c r="O27" t="n">
         <v>563.4435999999999</v>
@@ -17052,7 +17052,7 @@
         <v>982.2577</v>
       </c>
       <c r="O66" t="n">
-        <v>711.5056</v>
+        <v>711.5055</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>

--- a/rapporten/investeerder.xlsx
+++ b/rapporten/investeerder.xlsx
@@ -4155,7 +4155,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>9438.940000000001</v>
+        <v>9438.120000000001</v>
       </c>
       <c r="C16" s="2">
         <f>B16-B15</f>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Micron (MU)  ·  884,89 USD</t>
+          <t>Micron (MU)  ·  884,74 USD</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
     <row r="27" ht="22" customHeight="1">
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>Halfgeleider-ETF (SMH)  ·  522,83 USD</t>
+          <t>Halfgeleider-ETF (SMH)  ·  522,49 USD</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>AMD (AMD)  ·  505,18 USD</t>
+          <t>AMD (AMD)  ·  504,80 USD</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Gestegen: 6,1% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
+          <t>Gestegen: 6,0% in de laatste 3 maanden. Trend verzwakt: de koers is onder het 50-daags gemiddelde gezakt.</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6256</v>
       </c>
     </row>
     <row r="3">
@@ -5641,7 +5641,7 @@
         <v>1470.6326</v>
       </c>
       <c r="AD3" t="n">
-        <v>1535.0509</v>
+        <v>1535.051</v>
       </c>
       <c r="AE3" t="n">
         <v>1208.2668</v>
@@ -6339,7 +6339,7 @@
         <v>877.4319</v>
       </c>
       <c r="N7" t="n">
-        <v>970.7131000000001</v>
+        <v>970.713</v>
       </c>
       <c r="O7" t="n">
         <v>534.7758</v>
@@ -6757,7 +6757,7 @@
         <v>1564.9065</v>
       </c>
       <c r="AD9" t="n">
-        <v>1547.2469</v>
+        <v>1547.247</v>
       </c>
       <c r="AE9" t="n">
         <v>1227.0882</v>
@@ -7827,7 +7827,7 @@
         <v>936.9625</v>
       </c>
       <c r="N15" t="n">
-        <v>962.1174999999999</v>
+        <v>962.1174</v>
       </c>
       <c r="O15" t="n">
         <v>563.4435999999999</v>
@@ -15084,7 +15084,7 @@
         <v>982.2577</v>
       </c>
       <c r="O54" t="n">
-        <v>711.5056</v>
+        <v>711.5055</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -17301,22 +17301,22 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>883.04</v>
+        <v>884</v>
       </c>
       <c r="K66" t="n">
         <v>906.54</v>
       </c>
       <c r="L66" t="n">
-        <v>861.585</v>
+        <v>861.59</v>
       </c>
       <c r="M66" t="n">
-        <v>884.89</v>
+        <v>884.74</v>
       </c>
       <c r="N66" t="n">
-        <v>978.5952</v>
+        <v>978.5922</v>
       </c>
       <c r="O66" t="n">
-        <v>746.6257000000001</v>
+        <v>746.6249</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -17333,13 +17333,13 @@
         <v>511.63</v>
       </c>
       <c r="U66" t="n">
-        <v>522.83</v>
+        <v>522.49</v>
       </c>
       <c r="V66" t="n">
-        <v>572.6224</v>
+        <v>572.6156</v>
       </c>
       <c r="W66" t="n">
-        <v>519.5027</v>
+        <v>519.501</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -17393,22 +17393,22 @@
         </is>
       </c>
       <c r="AP66" t="n">
-        <v>510.12</v>
+        <v>508.53</v>
       </c>
       <c r="AQ66" t="n">
-        <v>520.3955999999999</v>
+        <v>520.4</v>
       </c>
       <c r="AR66" t="n">
-        <v>492.24</v>
+        <v>492.21</v>
       </c>
       <c r="AS66" t="n">
-        <v>505.18</v>
+        <v>504.8</v>
       </c>
       <c r="AT66" t="n">
-        <v>548.2978000000001</v>
+        <v>548.2902</v>
       </c>
       <c r="AU66" t="n">
-        <v>410.4906</v>
+        <v>410.4887</v>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
